--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3427,154 +3427,154 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>BERICHT</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Codepunkte</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>Prüfungen</v>
+        <v>Verstärkungskurve</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>Abonnieren</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>Schließen</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>sie@example.com</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>(optional)</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>Abbrechen</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="397">
@@ -3587,18 +3587,18 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="400">
@@ -3611,535 +3611,631 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>Fehler:</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>In XML konvertieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>Profil-ID</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>Tag-Name</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>Offset</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>Größe</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>Auffüllung</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>Typ</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>Array von {type}</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>Bytes</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>Profil ist gültig</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>Gültig</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>Warnung</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>Fehler</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>Unbekannt</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>Bestanden</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>Validierungsdetail</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>Feld</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>Aktueller Wert</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>Ungültig</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>Schließen</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>Einrückung</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3451,791 +3451,951 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Umgebung</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Erkennung…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Umgebung konnte nicht erkannt werden.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>HDR-Display</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>Vollbereich</v>
+        <v>Erweiterter Gamut</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>HDR-Canvas-Pfad</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>keiner</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>ja</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>BERICHT</v>
+        <v>nein</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>nicht gemeldet</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>Prüfungen</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfen</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Anzeigen</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Eingebettetes ICC-Profil lesen — kein Codec nötig</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>Abonnieren</v>
+        <v>Pixel anzeigen</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Heller als Weiß darstellen</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Von profiletool selbst dekodiert, also browserunabhängig</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>Schließen</v>
+        <v>Browser können nicht melden, wie viel HDR-Spielraum ein Display hat, nur ob ein HDR-Pfad existiert.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>sie@example.com</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>(optional)</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>Abbrechen</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>Abonnieren</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>Schließen</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>Fehler:</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>In XML konvertieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>In ICC konvertieren</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>ICC-Profil laden</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>Profil-ID</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>Tag-Name</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>Offset</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>Größe</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>Auffüllung</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>Typ</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>Array von {type}</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>Bytes</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>Profil ist gültig</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>Gültig</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>Warnung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>Fehler</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>Unbekannt</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>Bestanden</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>Validierungsdetail</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>Feld</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>Aktueller Wert</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>Ungültig</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>Schließen</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>Einrückung</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3459,943 +3459,975 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>Erkennung…</v>
+        <v>SDR-Rückfall wird angezeigt</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>Umgebung konnte nicht erkannt werden.</v>
+        <v>HDR-Profil in der Kette</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR-Display</v>
+        <v>Transformationen über ein HDR-Profil nutzen dessen AToB0Tag — das von Abschnitt 8.10.6 geforderte feste SDR-Rendering — da Abschnitt 8.10.1 keine TRC-Tags zulässt. Das Ergebnis ist dieser Rückfall, kein HDR-Verhalten.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>Erweiterter Gamut</v>
+        <v>Dies sind HDR-Profile ohne TRC-Tags; der Gamut wird daher aus dem AToB0Tag gebildet — dem festen SDR-Rendering, das Abschnitt 8.10.6 für Anwendungen ohne HDR-Verarbeitung verlangt. Es ist nicht der HDR-Gamut des Profils, der in einem begrenzten PCS nicht darstellbar ist.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>HDR-Canvas-Pfad</v>
+        <v>Erkennung…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>Umgebung konnte nicht erkannt werden.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>keiner</v>
+        <v>HDR-Display</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>ja</v>
+        <v>Erweiterter Gamut</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>nein</v>
+        <v>HDR-Canvas-Pfad</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>nicht gemeldet</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>Format</v>
+        <v>keiner</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>Prüfen</v>
+        <v>ja</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>Anzeigen</v>
+        <v>nein</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>nicht gemeldet</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>Eingebettetes ICC-Profil lesen — kein Codec nötig</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>Pixel anzeigen</v>
+        <v>Prüfen</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>Heller als Weiß darstellen</v>
+        <v>Anzeigen</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>Von profiletool selbst dekodiert, also browserunabhängig</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>Browser können nicht melden, wie viel HDR-Spielraum ein Display hat, nur ob ein HDR-Pfad existiert.</v>
+        <v>Eingebettetes ICC-Profil lesen — kein Codec nötig</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Pixel anzeigen</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Heller als Weiß darstellen</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Von profiletool selbst dekodiert, also browserunabhängig</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Browser können nicht melden, wie viel HDR-Spielraum ein Display hat, nur ob ein HDR-Pfad existiert.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>Vollbereich</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>BERICHT</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>Prüfungen</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>Abonnieren</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>Schließen</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>sie@example.com</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>(optional)</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>Abbrechen</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>Abonnieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>Schließen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>Fehler:</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>In XML konvertieren</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC-Profil laden</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>Profil-ID</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>Tag-Name</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>Offset</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>Größe</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>Auffüllung</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>Typ</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>Array von {type}</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>Bytes</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>Profil ist gültig</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>Gültig</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>Warnung</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>Fehler</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>Unbekannt</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>Bestanden</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>Validierungsdetail</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>Feld</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>Aktueller Wert</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>Ungültig</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>Schließen</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>Einrückung</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3643,791 +3643,871 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Browser-Flags</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>aktiv</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>nicht aktiviert</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>hier nicht erkennbar</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>Vollbereich</v>
+        <v>Für HDR-Darstellung in diesem Browser nötig: ohne WebGPU ist das HDR-Canvas der einzige Weg. Die Profilprüfung funktioniert auch ohne.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Optional: HDR kann über WebGPU dargestellt werden, dies ergänzt aber den HDR-Canvas-Weg und lässt profiletool den echten HDR-Spielraum des Bildschirms lesen.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Webseiten können keine Flag-Seiten öffnen. Fügen Sie dies in die Adressleiste ein, stellen Sie Enabled ein und starten Sie den Browser neu.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Kopieren</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Kopiert</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>BERICHT</v>
+        <v>Kopieren fehlgeschlagen — Adresse markieren und kopieren.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>Prüfungen</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>Abonnieren</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>Schließen</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>sie@example.com</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>(optional)</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>Abbrechen</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>Abonnieren</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>Schließen</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>Fehler:</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>In XML konvertieren</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>Profil-ID</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>Tag-Name</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>Offset</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>Größe</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>Auffüllung</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>Typ</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>Array von {type}</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>Bytes</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>Profil ist gültig</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>Gültig</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>Warnung</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>Fehler</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>Unbekannt</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>Bestanden</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>Validierungsdetail</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>Feld</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>Aktueller Wert</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>Ungültig</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>Schließen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>Einrückung</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Browser können nicht melden, wie viel HDR-Spielraum ein Display hat, nur ob ein HDR-Pfad existiert.</v>
+        <v>Dieser Browser hat den HDR-Spielraum des Displays nicht gemeldet, nur ob ein HDR-Pfad existiert.</v>
       </c>
     </row>
     <row r="405">
@@ -3723,791 +3723,927 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Pixelverhältnis</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Aktueller Monitor</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>ohne Namen</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>primär</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>Vollbereich</v>
+        <v>eingebaut</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>HDR-Spielraum</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>von diesem Browser nicht bereitgestellt</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Genau so angezeigt, wie der Browser ihn meldet. Die Einheit ist noch nicht standardisiert; ein SDR-Bildschirm meldete 0.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>BERICHT</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>Prüfungen</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>Abonnieren</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>Schließen</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>sie@example.com</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>(optional)</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>Abbrechen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>Abonnieren</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>Schließen</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>Fehler:</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>In XML konvertieren</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>In ICC konvertieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>Profil-ID</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>Tag-Name</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>Offset</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>Größe</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Auffüllung</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>Typ</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>Array von {type}</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>Bytes</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>Profil ist gültig</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>Gültig</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>Warnung</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>Fehler</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>Unbekannt</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>Bestanden</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>Validierungsdetail</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>Feld</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>Aktueller Wert</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>Ungültig</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>Schließen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>Einrückung</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3779,871 +3779,879 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>Genau so angezeigt, wie der Browser ihn meldet. Die Einheit ist noch nicht standardisiert; ein SDR-Bildschirm meldete 0.</v>
+        <v>Chromium meldet dies in Blendenstufen: log₂ aus Spitzenhelligkeit des Displays ÷ SDR-Weißpegel. Unter Windows wird der Wert nur aktualisiert, wenn Chrome das Display neu einliest – Fenster auf einen anderen Bildschirm verschoben oder Chrome wieder aktiviert –, nicht bei Helligkeitsänderungen.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>{stops} Blendenstufen (≈{ratio}× SDR-Weiß)</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>Displays erkennen</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>Vollbereich</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>BERICHT</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>sie@example.com</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>(optional)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>Abbrechen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>Abonnieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>Schließen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>Fehler:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3795,863 +3795,1383 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>Displays erkennen</v>
+        <v>Verstärkung bei einem Display-Spielraum</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Ein HDR-Bild auf diesem Display ansehen. Dateien, die der Browser dekodieren kann, zeigt der Browser selbst an; OpenEXR wird von profiletool dekodiert und dargestellt.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>HDR-Bild hier ablegen oder klicken, um eines auszuwählen</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>OpenEXR, AVIF, JPEG (auch Gain-Map-JPEG), PNG – und HEIC in Safari.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Anderes wählen</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Eingebettetes ICC-Profil</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>keins – OpenEXR gibt Farbe über Chromatizitäten an</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>wird geprüft…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>keins</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Im Tab „Profil“ öffnen</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Gain-Map</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>Vollbereich</v>
+        <v>erkannt, nicht dekodiert</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Das ist kein Bild. Profile über den Profilbereich laden.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Kein Bildformat, das profiletool erkennt.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>TIFF-Pixel werden hier noch nicht angezeigt: Browser dekodieren kein TIFF, und wie HDR in einem 16-Bit-TIFF kodiert wird, ist noch offen (Phase 4.3). Das eingebettete Profil kann untersucht werden.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Dieses Bild kann hier nicht angezeigt werden:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>BERICHT</v>
+        <v>Das eingebettete Profil kann trotzdem untersucht werden.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Angezeigt von</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>Prüfungen</v>
+        <v>dem Browser</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>HDR-Display</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Browser ignorieren HDR, das nur durch ein eingebettetes ICC-Profil angegeben ist; dieses Bild kann daher matt und flach wirken.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Dieser Browser kann ein Bild nicht zwischen SDR und HDR umschalten; es wird so gezeigt, wie der Browser es darstellt.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>Abonnieren</v>
+        <v>Der Browser konnte dieses Bild nicht dekodieren.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Ausgabe</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>HDR-Canvas (float16)</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>Schließen</v>
+        <v>WebGPU (erweiterter Bereich)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>SDR-Canvas (Tone-Mapping)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>sie@example.com</v>
+        <v>Hellstes Pixel</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>{n}× SDR-Weiß</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>(optional)</v>
+        <v>Chromatizitäten</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>nicht angegeben – Rec. 709 angenommen</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>{from} ist hier nicht verfügbar ({why}); die nächste Ausgabe wird verwendet.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>Abbrechen</v>
+        <v>Diese Ausgabe kann keine Werte heller als Weiß transportieren; die SDR-Darstellung mit Tone-Mapping wird gezeigt.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>Abonnieren</v>
+        <v>Belichtung</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>{n} Blendenstufen</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Dekodierung fehlgeschlagen:</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>Schließen</v>
+        <v>Wird dekodiert…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Dynamikumfang</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Dieser Browser bietet nur die beiden Enden, keine Mischung.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>Fehler:</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>In XML konvertieren</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>Profil-ID</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>Tag-Name</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>Offset</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>Größe</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>Auffüllung</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>Typ</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>Array von {type}</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>Bytes</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>Profil ist gültig</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>Gültig</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>Warnung</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>Fehler</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>Unbekannt</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>Bestanden</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>Validierungsdetail</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>Ausgelöst durch</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>Feld</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>Aktueller Wert</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>Ungültig</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>Schließen</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>Einrückung</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>Datenschutzhinweis</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>Fehler:</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>In XML konvertieren</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>In JSON konvertieren</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>In ICC konvertieren</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>Konvertiere in XML…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>Konvertiere in JSON…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>Konvertiere in ICC…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>ICC-Profil laden</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>Keine Tags gefunden.</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>Tag-Name</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>Größe</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>Auffüllung</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>Bytes seit dem Laden geändert</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>Array von {type}</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>(Kein Inhalt)</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>Bytes</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>Lade vollständige Beschreibung…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>Keine Validierungsausgabe</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>Profil ist gültig</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>Profil hat Warnung(en)</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>Profil ist nicht konform</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>Kritischer Validierungsfehler</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>Unbekannter Validierungsstatus</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4139,1039 +4139,1175 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>von profiletool selbst dekodiert, daher browserunabhängig</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>Display-Spielraum</v>
+        <v>dieser Browser dekodiert es</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>dieser Browser dekodiert es nicht</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>Basis</v>
+        <v>HEIC-Anzeige erfordert Safari oder einen anderen WebKit-Browser – Chrome und Firefox dekodieren HEIC auf keiner Plattform, auch nicht unter macOS</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>JPEG-XL-Anzeige erfordert Safari; andere Browser unterstützen es noch nicht</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>auf eine spätere Version verschoben</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>dieses Display meldet keinen HDR-Pfad, daher wird HDR per Tone-Mapping als SDR dargestellt</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>dieser Browser bietet keinen HDR-Canvas-Pfad (float16-Canvas oder WebGPU nötig)</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Firefox zeigt keine HDR-Bilder und liest keine Gain-Maps; HDR-Inhalte werden als SDR gezeigt</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>die Untersuchung braucht nur das Parsen des Containers, keinen Codec</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>HDR-Display und HDR-Canvas-Pfad sind beide verfügbar</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>unbekanntes Format</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>{browser} unter {os}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>{name} · HDR-Display erkannt</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>{name} · SDR-Display</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>WebGPU hat Tone-Mapping „{mode}“ angewendet; die Ausgabe ist daher auf SDR begrenzt</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Dieser Browser meldet das angewendete WebGPU-Tone-Mapping nicht; HDR-Ausgabe ist unbestätigt</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>Keine Änderung</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>Displays erkennen</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>Vollbereich</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>BERICHT</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>Prüfungen</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>Abonnieren</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>Schließen</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>sie@example.com</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>(optional)</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>Abbrechen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>Abonnieren</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>Schließen</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>Fehler:</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>In XML konvertieren</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>In ICC konvertieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>Profil-ID</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>Tag-Name</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>Offset</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>Größe</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>Auffüllung</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>Typ</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>Array von {type}</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>Bytes</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>Profil ist gültig</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>Gültig</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>Warnung</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>Fehler</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>Unbekannt</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>Bestanden</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>Validierungsdetail</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>Feld</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>Aktueller Wert</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>Ungültig</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>Schließen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>Einrückung</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4275,1039 +4275,1143 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>Display-Spielraum</v>
+        <v>{r}× SDR-Weiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>1× – SDR-Display</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>Basis</v>
+        <v>unbekannt</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Dieses Display meldet kein HDR, daher zeigt der Browser das Bild an beiden Enden als SDR.</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Dieses Display meldet kein HDR, daher wird alles heller als SDR-Weiß abgeschnitten. „An Display anpassen“ zeigt stattdessen die Darstellung mit Tone-Mapping.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Dieses Bild verlangt {img}× SDR-Weiß, dieses Display zeigt aber nur bis {disp}×; hellere Werte werden abgeschnitten. „An Display anpassen“ lässt sie stattdessen sanft in die Display-Spitze auslaufen.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>An Display anpassen</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>keine Grenze</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Grenze {n} Blendenstufen ({r}×)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>SDR-Weiß</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>Keine Änderung</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>Displays erkennen</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>Vollbereich</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>BERICHT</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>Prüfungen</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>Abonnieren</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>Schließen</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>sie@example.com</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>(optional)</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>Abbrechen</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>Fehler:</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>In XML konvertieren</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>Profil-ID</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>Tag-Name</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>Offset</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>Größe</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>Auffüllung</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>Typ</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>Array von {type}</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>Bytes</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>Profil ist gültig</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>Gültig</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>Warnung</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>Fehler</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>Unbekannt</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>Bestanden</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>Validierungsdetail</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>Feld</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>Aktueller Wert</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>Ungültig</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>Schließen</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>Einrückung</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4379,1039 +4379,1055 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>SDR-Weiß-Feld</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>Display-Spielraum</v>
+        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Basis</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>Keine Änderung</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>Displays erkennen</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>Vollbereich</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>BERICHT</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>Prüfungen</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>Abonnieren</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>sie@example.com</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>(optional)</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>Abbrechen</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>Abonnieren</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>Schließen</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>Fehler:</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>In XML konvertieren</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>Profil-ID</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>Tag-Name</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>Offset</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>Größe</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>Auffüllung</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>Typ</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>Array von {type}</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>Bytes</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>Profil ist gültig</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>Gültig</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>Warnung</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>Fehler</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>Unbekannt</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>Bestanden</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>Validierungsdetail</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>Feld</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>Aktueller Wert</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>Ungültig</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>Schließen</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4395,1039 +4395,1223 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>Profil zuweisen</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>Display-Spielraum</v>
+        <v>Keins – was die Datei angibt</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>Eingebettetes Profil ({n} B)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>Basis</v>
+        <v>HDR-Profile im Pool</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>eingebettetes Profil</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Pfad des Farbmoduls</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>HDR-Pfad, keine Verstärkungskurve</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Übertragung</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Ziel-Spielraum</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Tone-Mapping</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Auto (Rangfolge nach 8.10.3)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Verstärkungskurve (HAGC)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Aus – wie ein CMM vor der Änderung</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>Keine Änderung</v>
+        <v>Profil wird angewendet…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>OpenEXR enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>Displays erkennen</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>Vollbereich</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>BERICHT</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>Prüfungen</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>Abonnieren</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>Schließen</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>sie@example.com</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>(optional)</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>Abbrechen</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>Abonnieren</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>Schließen</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>Fehler:</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>In XML konvertieren</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC-Profil laden</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>Profil-ID</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>Tag-Name</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>Offset</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>Größe</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>Auffüllung</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>Typ</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>Array von {type}</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>Bytes</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>Profil ist gültig</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>Gültig</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>Warnung</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>Fehler</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>Unbekannt</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>Bestanden</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>Validierungsdetail</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>Feld</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>Aktueller Wert</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>Ungültig</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>Schließen</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>Einrückung</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4579,1039 +4579,1103 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>HDR-Profile</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>Display-Spielraum</v>
+        <v>Lineare Übertragung</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>Nichtlineare Übertragung (PQ, HLG)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>Basis</v>
+        <v>HDR-Profile – lineare Übertragung</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>OpenEXR enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>Keine Änderung</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>Displays erkennen</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>Vollbereich</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>BERICHT</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>Prüfungen</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>Abonnieren</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>Schließen</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>sie@example.com</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>(optional)</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>Abbrechen</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>Abonnieren</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>Schließen</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>Fehler:</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>In XML konvertieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>Profil-ID</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>Tag-Name</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>Offset</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>Größe</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>Auffüllung</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>Typ</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>Array von {type}</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>Bytes</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>Profil ist gültig</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>Gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>Warnung</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>Fehler</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>Unbekannt</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>Bestanden</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>Validierungsdetail</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>Feld</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>Aktueller Wert</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>Ungültig</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>Schließen</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>Einrückung</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Ein HDR-Bild auf diesem Display ansehen. Dateien, die der Browser dekodieren kann, zeigt der Browser selbst an; OpenEXR wird von profiletool dekodiert und dargestellt.</v>
+        <v>Ein HDR-Bild auf diesem Display ansehen. Dateien, die der Browser dekodieren kann, zeigt der Browser selbst an; OpenEXR und Radiance HDR werden von profiletool dekodiert und dargestellt.</v>
       </c>
     </row>
     <row r="427">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, AVIF, JPEG (auch Gain-Map-JPEG), PNG – und HEIC in Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (auch Gain-Map-JPEG), PNG – und HEIC in Safari.</v>
       </c>
     </row>
     <row r="429">
@@ -3867,1815 +3867,1823 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>wird geprüft…</v>
+        <v>keins – Radiance HDR gibt Farbe über seine PRIMARIES-Kopfzeile an</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>keins</v>
+        <v>wird geprüft…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>Im Tab „Profil“ öffnen</v>
+        <v>keins</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>Gain-Map</v>
+        <v>Im Tab „Profil“ öffnen</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>erkannt, nicht dekodiert</v>
+        <v>Gain-Map</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>Das ist kein Bild. Profile über den Profilbereich laden.</v>
+        <v>erkannt, nicht dekodiert</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>Kein Bildformat, das profiletool erkennt.</v>
+        <v>Das ist kein Bild. Profile über den Profilbereich laden.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>TIFF-Pixel werden hier noch nicht angezeigt: Browser dekodieren kein TIFF, und wie HDR in einem 16-Bit-TIFF kodiert wird, ist noch offen (Phase 4.3). Das eingebettete Profil kann untersucht werden.</v>
+        <v>Kein Bildformat, das profiletool erkennt.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>Dieses Bild kann hier nicht angezeigt werden:</v>
+        <v>TIFF-Pixel werden hier noch nicht angezeigt: Browser dekodieren kein TIFF, und wie HDR in einem 16-Bit-TIFF kodiert wird, ist noch offen (Phase 4.3). Das eingebettete Profil kann untersucht werden.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>Das eingebettete Profil kann trotzdem untersucht werden.</v>
+        <v>Dieses Bild kann hier nicht angezeigt werden:</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>Angezeigt von</v>
+        <v>Das eingebettete Profil kann trotzdem untersucht werden.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>dem Browser</v>
+        <v>Angezeigt von</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>dem Browser</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>HDR-Display</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>Browser ignorieren HDR, das nur durch ein eingebettetes ICC-Profil angegeben ist; dieses Bild kann daher matt und flach wirken.</v>
+        <v>HDR-Display</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>Dieser Browser kann ein Bild nicht zwischen SDR und HDR umschalten; es wird so gezeigt, wie der Browser es darstellt.</v>
+        <v>Browser ignorieren HDR, das nur durch ein eingebettetes ICC-Profil angegeben ist; dieses Bild kann daher matt und flach wirken.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>Der Browser konnte dieses Bild nicht dekodieren.</v>
+        <v>Dieser Browser kann ein Bild nicht zwischen SDR und HDR umschalten; es wird so gezeigt, wie der Browser es darstellt.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>Ausgabe</v>
+        <v>Der Browser konnte dieses Bild nicht dekodieren.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>HDR-Canvas (float16)</v>
+        <v>Ausgabe</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU (erweiterter Bereich)</v>
+        <v>HDR-Canvas (float16)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>SDR-Canvas (Tone-Mapping)</v>
+        <v>WebGPU (erweiterter Bereich)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>Größe</v>
+        <v>SDR-Canvas (Tone-Mapping)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>Hellstes Pixel</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>{n}× SDR-Weiß</v>
+        <v>Hellstes Pixel</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>Chromatizitäten</v>
+        <v>{n}× SDR-Weiß</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>nicht angegeben – Rec. 709 angenommen</v>
+        <v>Chromatizitäten</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from} ist hier nicht verfügbar ({why}); die nächste Ausgabe wird verwendet.</v>
+        <v>nicht angegeben – Rec. 709 angenommen</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>Diese Ausgabe kann keine Werte heller als Weiß transportieren; die SDR-Darstellung mit Tone-Mapping wird gezeigt.</v>
+        <v>{from} ist hier nicht verfügbar ({why}); die nächste Ausgabe wird verwendet.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>Belichtung</v>
+        <v>Diese Ausgabe kann keine Werte heller als Weiß transportieren; die SDR-Darstellung mit Tone-Mapping wird gezeigt.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} Blendenstufen</v>
+        <v>Belichtung</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>Dekodierung fehlgeschlagen:</v>
+        <v>{n} Blendenstufen</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>Wird dekodiert…</v>
+        <v>Dekodierung fehlgeschlagen:</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>Dynamikumfang</v>
+        <v>Wird dekodiert…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>Dieser Browser bietet nur die beiden Enden, keine Mischung.</v>
+        <v>Dynamikumfang</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>von profiletool selbst dekodiert, daher browserunabhängig</v>
+        <v>Dieser Browser bietet nur die beiden Enden, keine Mischung.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>dieser Browser dekodiert es</v>
+        <v>von profiletool selbst dekodiert, daher browserunabhängig</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>dieser Browser dekodiert es nicht</v>
+        <v>dieser Browser dekodiert es</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>HEIC-Anzeige erfordert Safari oder einen anderen WebKit-Browser – Chrome und Firefox dekodieren HEIC auf keiner Plattform, auch nicht unter macOS</v>
+        <v>dieser Browser dekodiert es nicht</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>JPEG-XL-Anzeige erfordert Safari; andere Browser unterstützen es noch nicht</v>
+        <v>HEIC-Anzeige erfordert Safari oder einen anderen WebKit-Browser – Chrome und Firefox dekodieren HEIC auf keiner Plattform, auch nicht unter macOS</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>auf eine spätere Version verschoben</v>
+        <v>JPEG-XL-Anzeige erfordert Safari; andere Browser unterstützen es noch nicht</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>dieses Display meldet keinen HDR-Pfad, daher wird HDR per Tone-Mapping als SDR dargestellt</v>
+        <v>auf eine spätere Version verschoben</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>dieser Browser bietet keinen HDR-Canvas-Pfad (float16-Canvas oder WebGPU nötig)</v>
+        <v>dieses Display meldet keinen HDR-Pfad, daher wird HDR per Tone-Mapping als SDR dargestellt</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox zeigt keine HDR-Bilder und liest keine Gain-Maps; HDR-Inhalte werden als SDR gezeigt</v>
+        <v>dieser Browser bietet keinen HDR-Canvas-Pfad (float16-Canvas oder WebGPU nötig)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>die Untersuchung braucht nur das Parsen des Containers, keinen Codec</v>
+        <v>Firefox zeigt keine HDR-Bilder und liest keine Gain-Maps; HDR-Inhalte werden als SDR gezeigt</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>HDR-Display und HDR-Canvas-Pfad sind beide verfügbar</v>
+        <v>die Untersuchung braucht nur das Parsen des Containers, keinen Codec</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>unbekanntes Format</v>
+        <v>HDR-Display und HDR-Canvas-Pfad sind beide verfügbar</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{browser} unter {os}</v>
+        <v>unbekanntes Format</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · HDR-Display erkannt</v>
+        <v>{browser} unter {os}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · SDR-Display</v>
+        <v>{name} · HDR-Display erkannt</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU hat Tone-Mapping „{mode}“ angewendet; die Ausgabe ist daher auf SDR begrenzt</v>
+        <v>{name} · SDR-Display</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>Dieser Browser meldet das angewendete WebGPU-Tone-Mapping nicht; HDR-Ausgabe ist unbestätigt</v>
+        <v>WebGPU hat Tone-Mapping „{mode}“ angewendet; die Ausgabe ist daher auf SDR begrenzt</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>Display-Spitze</v>
+        <v>Dieser Browser meldet das angewendete WebGPU-Tone-Mapping nicht; HDR-Ausgabe ist unbestätigt</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>{r}× SDR-Weiß ({n} Blendenstufen)</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× – SDR-Display</v>
+        <v>{r}× SDR-Weiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>unbekannt</v>
+        <v>1× – SDR-Display</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>Dieses Display meldet kein HDR, daher zeigt der Browser das Bild an beiden Enden als SDR.</v>
+        <v>unbekannt</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>Dieses Display meldet kein HDR, daher wird alles heller als SDR-Weiß abgeschnitten. „An Display anpassen“ zeigt stattdessen die Darstellung mit Tone-Mapping.</v>
+        <v>Dieses Display meldet kein HDR, daher zeigt der Browser das Bild an beiden Enden als SDR.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Dieses Bild verlangt {img}× SDR-Weiß, dieses Display zeigt aber nur bis {disp}×; hellere Werte werden abgeschnitten. „An Display anpassen“ lässt sie stattdessen sanft in die Display-Spitze auslaufen.</v>
+        <v>Dieses Display meldet kein HDR, daher wird alles heller als SDR-Weiß abgeschnitten. „An Display anpassen“ zeigt stattdessen die Darstellung mit Tone-Mapping.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>An Display anpassen</v>
+        <v>Dieses Bild verlangt {img}× SDR-Weiß, dieses Display zeigt aber nur bis {disp}×; hellere Werte werden abgeschnitten. „An Display anpassen“ lässt sie stattdessen sanft in die Display-Spitze auslaufen.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
+        <v>An Display anpassen</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>keine Grenze</v>
+        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>Grenze {n} Blendenstufen ({r}×)</v>
+        <v>keine Grenze</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>SDR-Weiß</v>
+        <v>Grenze {n} Blendenstufen ({r}×)</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
+        <v>SDR-Weiß</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>SDR-Weiß-Feld</v>
+        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
+        <v>SDR-Weiß-Feld</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>Profil zuweisen</v>
+        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>Keins – was die Datei angibt</v>
+        <v>Profil zuweisen</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>Eingebettetes Profil ({n} B)</v>
+        <v>Keins – was die Datei angibt</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>HDR-Profile im Pool</v>
+        <v>Eingebettetes Profil ({n} B)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>Profil</v>
+        <v>HDR-Profile im Pool</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>eingebettetes Profil</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>Pfad des Farbmoduls</v>
+        <v>eingebettetes Profil</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
+        <v>Pfad des Farbmoduls</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR-Pfad, keine Verstärkungskurve</v>
+        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
+        <v>HDR-Pfad, keine Verstärkungskurve</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>Übertragung</v>
+        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>HDR-Referenzweiß</v>
+        <v>Übertragung</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>Ziel-Spielraum</v>
+        <v>HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
+        <v>Ziel-Spielraum</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>Tone-Mapping</v>
+        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>Auto (Rangfolge nach 8.10.3)</v>
+        <v>Tone-Mapping</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>Verstärkungskurve (HAGC)</v>
+        <v>Auto (Rangfolge nach 8.10.3)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
+        <v>Verstärkungskurve (HAGC)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>Aus – wie ein CMM vor der Änderung</v>
+        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>Profil wird angewendet…</v>
+        <v>Aus – wie ein CMM vor der Änderung</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
+        <v>Profil wird angewendet…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
+        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
+        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR-Profile</v>
+        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>Lineare Übertragung</v>
+        <v>HDR-Profile</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>Nichtlineare Übertragung (PQ, HLG)</v>
+        <v>Lineare Übertragung</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>HDR-Profile – lineare Übertragung</v>
+        <v>Nichtlineare Übertragung (PQ, HLG)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
+        <v>HDR-Profile – lineare Übertragung</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
+        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
+        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
+        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>Display-Spielraum</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>Basis</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>Keine Änderung</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>Displays erkennen</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>Vollbereich</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>BERICHT</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>sie@example.com</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>(optional)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>Abbrechen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>Abonnieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>Schließen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>Fehler:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4347,1343 +4347,1431 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
+        <v>Bilddetails</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>keine Grenze</v>
+        <v>nicht verfügbar – der Browser stellt dieses Bild dar und kann es nicht auf eine feste Spitze begrenzen</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>Grenze {n} Blendenstufen ({r}×)</v>
+        <v>nicht verfügbar – diese Ausgabe zeigt nichts über SDR-Weiß</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>SDR-Weiß</v>
+        <v>nicht verfügbar – die Spitzenhelligkeit dieses Displays ist unbekannt</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
+        <v>Vergrößern</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>SDR-Weiß-Feld</v>
+        <v>Verkleinern</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
+        <v>Bild einpassen</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>Profil zuweisen</v>
+        <v>Echte Pixel (1:1)</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>Keins – was die Datei angibt</v>
+        <v>Ziehen zum Verschieben · Strg+Mausrad zum Zoomen · Doppelklick zum Zurücksetzen</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>Eingebettetes Profil ({n} B)</v>
+        <v>Ziehen, um den Bildbereich zu ändern; Doppelklick stellt die Standardgröße wieder her</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>HDR-Profile im Pool</v>
+        <v>Bildansicht</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>Profil</v>
+        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>eingebettetes Profil</v>
+        <v>keine Grenze</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>Pfad des Farbmoduls</v>
+        <v>Grenze {n} Blendenstufen ({r}×)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
+        <v>SDR-Weiß</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>HDR-Pfad, keine Verstärkungskurve</v>
+        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
+        <v>SDR-Weiß-Feld</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>Übertragung</v>
+        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>HDR-Referenzweiß</v>
+        <v>Profil zuweisen</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>Ziel-Spielraum</v>
+        <v>Keins – was die Datei angibt</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
+        <v>Eingebettetes Profil ({n} B)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>Tone-Mapping</v>
+        <v>HDR-Profile im Pool</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>Auto (Rangfolge nach 8.10.3)</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>Verstärkungskurve (HAGC)</v>
+        <v>eingebettetes Profil</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
+        <v>Pfad des Farbmoduls</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>Aus – wie ein CMM vor der Änderung</v>
+        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>Profil wird angewendet…</v>
+        <v>HDR-Pfad, keine Verstärkungskurve</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
+        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
+        <v>Übertragung</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
+        <v>HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR-Profile</v>
+        <v>Ziel-Spielraum</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>Lineare Übertragung</v>
+        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>Nichtlineare Übertragung (PQ, HLG)</v>
+        <v>Tone-Mapping</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR-Profile – lineare Übertragung</v>
+        <v>Auto (Rangfolge nach 8.10.3)</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
+        <v>Verstärkungskurve (HAGC)</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
+        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
+        <v>Aus – wie ein CMM vor der Änderung</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
+        <v>Profil wird angewendet…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>Display-Spielraum</v>
+        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>Basis</v>
+        <v>HDR-Profile</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Lineare Übertragung</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Nichtlineare Übertragung (PQ, HLG)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>HDR-Profile – lineare Übertragung</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>Keine Änderung</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>Displays erkennen</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>Vollbereich</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>BERICHT</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>Prüfungen</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>Abonnieren</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>Schließen</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>sie@example.com</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>(optional)</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Abbrechen</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>Abonnieren</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>Schließen</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>Fehler:</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>In XML konvertieren</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>Profil-ID</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>Tag-Name</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>Offset</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>Größe</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>Auffüllung</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>Typ</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>Array von {type}</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>Bytes</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>Profil ist gültig</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>Gültig</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>Warnung</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>Fehler</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>Unbekannt</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>Bestanden</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>Validierungsdetail</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>Feld</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>Aktueller Wert</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>Ungültig</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>Schließen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>Einrückung</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4771,1007 +4771,1191 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Vorschau durch das Farbmodul</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Tonemapping für {h} Blenden</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Referenzweiß</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Vorschau nicht verfügbar: {why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Verstärkung über alle Headrooms</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Display-Headroom (Blenden)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Verstärkung (Blenden)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Kurve im Tag</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>Keine Änderung</v>
+        <v>Regler</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Eingang = Display-Spitze</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Graue Tonkurven nach Headroom</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>Displays erkennen</v>
+        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>{h} Blenden</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>{h} Blenden (Basis)</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Bei {h} Blenden (Regler)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>Vollbereich</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>BERICHT</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>Prüfungen</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>Abonnieren</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>Schließen</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>sie@example.com</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>(optional)</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>Abbrechen</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>Abonnieren</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>Schließen</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>Fehler:</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>In XML konvertieren</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>ICC-Profil laden</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>Profil-ID</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>Tag-Name</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Offset</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>Größe</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>Auffüllung</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>Typ</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>Array von {type}</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>Bytes</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>Profil ist gültig</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>Gültig</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>Warnung</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>Fehler</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>Unbekannt</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>Bestanden</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>Validierungsdetail</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>Feld</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>Aktueller Wert</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>Ungültig</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>Schließen</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>Einrückung</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4587,1375 +4587,1431 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>Ziel-Spielraum</v>
+        <v>Lineare Werte</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
+        <v>Datei 1,0 = HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>Tone-Mapping</v>
+        <v>Datei 1,0 = 1 cd/m² (ICC.1 Abschnitt 8.10.2 a)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>Auto (Rangfolge nach 8.10.3)</v>
+        <v>OpenEXR- und Radiance-HDR-Dateien legen SDR-Weiß üblicherweise auf 1,0, während eine lineare ICC-Übertragung 1,0 als 1 cd/m² liest. Standardmäßig wird die Datei so skaliert, dass ihre 1,0 auf dem HDR-Referenzweiß des Profils liegt.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>Verstärkungskurve (HAGC)</v>
+        <v>Eingangsskalierung</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
+        <v>×{w} – Datei 1,0 = Referenzweiß</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>Aus – wie ein CMM vor der Änderung</v>
+        <v>keine – Datei 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>Profil wird angewendet…</v>
+        <v>Ziel-Spielraum</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
+        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
+        <v>Tone-Mapping</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
+        <v>Auto (Rangfolge nach 8.10.3)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>HDR-Profile</v>
+        <v>Verstärkungskurve (HAGC)</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>Lineare Übertragung</v>
+        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>Nichtlineare Übertragung (PQ, HLG)</v>
+        <v>Aus – wie ein CMM vor der Änderung</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>HDR-Profile – lineare Übertragung</v>
+        <v>Profil wird angewendet…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
+        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
+        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
+        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
+        <v>HDR-Profile</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>Lineare Übertragung</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>Display-Spielraum</v>
+        <v>Nichtlineare Übertragung (PQ, HLG)</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>HDR-Profile – lineare Übertragung</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>Basis</v>
+        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>Vorschau durch das Farbmodul</v>
+        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
+        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>Tonemapping für {h} Blenden</v>
+        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>Referenzweiß</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>Display-Spitze</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>Vorschau nicht verfügbar: {why}</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
+        <v>Vorschau durch das Farbmodul</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>Verstärkung über alle Headrooms</v>
+        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
+        <v>Tonemapping für {h} Blenden</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>Display-Headroom (Blenden)</v>
+        <v>Referenzweiß</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>Verstärkung (Blenden)</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>Kurve im Tag</v>
+        <v>Vorschau nicht verfügbar: {why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Basis</v>
+        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>Regler</v>
+        <v>Verstärkung über alle Headrooms</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>Eingang = Display-Spitze</v>
+        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>Graue Tonkurven nach Headroom</v>
+        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
+        <v>Display-Headroom (Blenden)</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Verstärkung (Blenden)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} Blenden</v>
+        <v>Kurve im Tag</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} Blenden (Basis)</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>Bei {h} Blenden (Regler)</v>
+        <v>Regler</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Eingang = Display-Spitze</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Graue Tonkurven nach Headroom</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>{h} Blenden</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>{h} Blenden (Basis)</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Bei {h} Blenden (Regler)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>Keine Änderung</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>Displays erkennen</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>Display-Ereignisse</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>Vollbereich</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>BERICHT</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>Prüfungen</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>Abonnieren</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>Schließen</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>sie@example.com</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>(optional)</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>Abbrechen</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>Abonnieren</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>Schließen</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>Fehler:</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>In XML konvertieren</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>Profil-ID</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>Tag-Name</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>Offset</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>Größe</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>Auffüllung</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>Typ</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>Array von {type}</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>Bytes</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>Profil ist gültig</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Gültig</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>Warnung</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>Fehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>Unbekannt</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Validierungsdetail</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>Feld</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>Aktueller Wert</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>Ungültig</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>Schließen</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>Einrückung</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4123,1895 +4123,1935 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>Wird dekodiert…</v>
+        <v>Diese Datei ist {size} MB groß; der HDR-Tab öffnet Bilder bis {max} MB.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>Dynamikumfang</v>
+        <v>Profil konnte nicht angewendet werden:</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>Dieser Browser bietet nur die beiden Enden, keine Mischung.</v>
+        <v>Bild konnte nicht gezeichnet werden:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>von profiletool selbst dekodiert, daher browserunabhängig</v>
+        <v>(diese Primärfarben definieren keinen Farbraum – ignoriert, Rec. 709 verwendet)</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>dieser Browser dekodiert es</v>
+        <v>das Profil eines JPEG XL ist im Codestream komprimiert, den profiletool noch nicht dekomprimiert</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>dieser Browser dekodiert es nicht</v>
+        <v>Wird dekodiert…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>HEIC-Anzeige erfordert Safari oder einen anderen WebKit-Browser – Chrome und Firefox dekodieren HEIC auf keiner Plattform, auch nicht unter macOS</v>
+        <v>Dynamikumfang</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>JPEG-XL-Anzeige erfordert Safari; andere Browser unterstützen es noch nicht</v>
+        <v>Dieser Browser bietet nur die beiden Enden, keine Mischung.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>auf eine spätere Version verschoben</v>
+        <v>von profiletool selbst dekodiert, daher browserunabhängig</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>dieses Display meldet keinen HDR-Pfad, daher wird HDR per Tone-Mapping als SDR dargestellt</v>
+        <v>dieser Browser dekodiert es</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>dieser Browser bietet keinen HDR-Canvas-Pfad (float16-Canvas oder WebGPU nötig)</v>
+        <v>dieser Browser dekodiert es nicht</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox zeigt keine HDR-Bilder und liest keine Gain-Maps; HDR-Inhalte werden als SDR gezeigt</v>
+        <v>HEIC-Anzeige erfordert Safari oder einen anderen WebKit-Browser – Chrome und Firefox dekodieren HEIC auf keiner Plattform, auch nicht unter macOS</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>die Untersuchung braucht nur das Parsen des Containers, keinen Codec</v>
+        <v>JPEG-XL-Anzeige erfordert Safari; andere Browser unterstützen es noch nicht</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>HDR-Display und HDR-Canvas-Pfad sind beide verfügbar</v>
+        <v>auf eine spätere Version verschoben</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>unbekanntes Format</v>
+        <v>dieses Display meldet keinen HDR-Pfad, daher wird HDR per Tone-Mapping als SDR dargestellt</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{browser} unter {os}</v>
+        <v>dieser Browser bietet keinen HDR-Canvas-Pfad (float16-Canvas oder WebGPU nötig)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · HDR-Display erkannt</v>
+        <v>Firefox zeigt keine HDR-Bilder und liest keine Gain-Maps; HDR-Inhalte werden als SDR gezeigt</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · SDR-Display</v>
+        <v>die Untersuchung braucht nur das Parsen des Containers, keinen Codec</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU hat Tone-Mapping „{mode}“ angewendet; die Ausgabe ist daher auf SDR begrenzt</v>
+        <v>HDR-Display und HDR-Canvas-Pfad sind beide verfügbar</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>Dieser Browser meldet das angewendete WebGPU-Tone-Mapping nicht; HDR-Ausgabe ist unbestätigt</v>
+        <v>unbekanntes Format</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>Display-Spitze</v>
+        <v>{browser} unter {os}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>{r}× SDR-Weiß ({n} Blendenstufen)</v>
+        <v>{name} · HDR-Display erkannt</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× – SDR-Display</v>
+        <v>{name} · SDR-Display</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>unbekannt</v>
+        <v>WebGPU hat Tone-Mapping „{mode}“ angewendet; die Ausgabe ist daher auf SDR begrenzt</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>Dieses Display meldet kein HDR, daher zeigt der Browser das Bild an beiden Enden als SDR.</v>
+        <v>Dieser Browser meldet das angewendete WebGPU-Tone-Mapping nicht; HDR-Ausgabe ist unbestätigt</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>Dieses Display meldet kein HDR, daher wird alles heller als SDR-Weiß abgeschnitten. „An Display anpassen“ zeigt stattdessen die Darstellung mit Tone-Mapping.</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>Dieses Bild verlangt {img}× SDR-Weiß, dieses Display zeigt aber nur bis {disp}×; hellere Werte werden abgeschnitten. „An Display anpassen“ lässt sie stattdessen sanft in die Display-Spitze auslaufen.</v>
+        <v>{r}× SDR-Weiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>An Display anpassen</v>
+        <v>1× – SDR-Display</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>Bilddetails</v>
+        <v>unbekannt</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>nicht verfügbar – der Browser stellt dieses Bild dar und kann es nicht auf eine feste Spitze begrenzen</v>
+        <v>Dieses Display meldet kein HDR, daher zeigt der Browser das Bild an beiden Enden als SDR.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>nicht verfügbar – diese Ausgabe zeigt nichts über SDR-Weiß</v>
+        <v>Dieses Display meldet kein HDR, daher wird alles heller als SDR-Weiß abgeschnitten. „An Display anpassen“ zeigt stattdessen die Darstellung mit Tone-Mapping.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>nicht verfügbar – die Spitzenhelligkeit dieses Displays ist unbekannt</v>
+        <v>Dieses Bild verlangt {img}× SDR-Weiß, dieses Display zeigt aber nur bis {disp}×; hellere Werte werden abgeschnitten. „An Display anpassen“ lässt sie stattdessen sanft in die Display-Spitze auslaufen.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>Vergrößern</v>
+        <v>An Display anpassen</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>Verkleinern</v>
+        <v>Bilddetails</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>Bild einpassen</v>
+        <v>nicht verfügbar – der Browser stellt dieses Bild dar und kann es nicht auf eine feste Spitze begrenzen</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>Echte Pixel (1:1)</v>
+        <v>nicht verfügbar – diese Ausgabe zeigt nichts über SDR-Weiß</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>Ziehen zum Verschieben · Strg+Mausrad zum Zoomen · Doppelklick zum Zurücksetzen</v>
+        <v>nicht verfügbar – die Spitzenhelligkeit dieses Displays ist unbekannt</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>Ziehen, um den Bildbereich zu ändern; Doppelklick stellt die Standardgröße wieder her</v>
+        <v>Vergrößern</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>Bildansicht</v>
+        <v>Verkleinern</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
+        <v>Bild einpassen</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>keine Grenze</v>
+        <v>Echte Pixel (1:1)</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>Grenze {n} Blendenstufen ({r}×)</v>
+        <v>Ziehen zum Verschieben · Strg+Mausrad zum Zoomen · Doppelklick zum Zurücksetzen</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>SDR-Weiß</v>
+        <v>Ziehen, um den Bildbereich zu ändern; Doppelklick stellt die Standardgröße wieder her</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
+        <v>Bildansicht</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>SDR-Weiß-Feld</v>
+        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
+        <v>keine Grenze</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>Profil zuweisen</v>
+        <v>Grenze {n} Blendenstufen ({r}×)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>Keins – was die Datei angibt</v>
+        <v>SDR-Weiß</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>Eingebettetes Profil ({n} B)</v>
+        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>HDR-Profile im Pool</v>
+        <v>SDR-Weiß-Feld</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>Profil</v>
+        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>eingebettetes Profil</v>
+        <v>Profil zuweisen</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>Pfad des Farbmoduls</v>
+        <v>Keins – was die Datei angibt</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
+        <v>Eingebettetes Profil ({n} B)</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR-Pfad, keine Verstärkungskurve</v>
+        <v>HDR-Profile im Pool</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>Übertragung</v>
+        <v>eingebettetes Profil</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR-Referenzweiß</v>
+        <v>Pfad des Farbmoduls</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>Lineare Werte</v>
+        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>Datei 1,0 = HDR-Referenzweiß</v>
+        <v>HDR-Pfad, keine Verstärkungskurve</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>Datei 1,0 = 1 cd/m² (ICC.1 Abschnitt 8.10.2 a)</v>
+        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>OpenEXR- und Radiance-HDR-Dateien legen SDR-Weiß üblicherweise auf 1,0, während eine lineare ICC-Übertragung 1,0 als 1 cd/m² liest. Standardmäßig wird die Datei so skaliert, dass ihre 1,0 auf dem HDR-Referenzweiß des Profils liegt.</v>
+        <v>Übertragung</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>Eingangsskalierung</v>
+        <v>HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} – Datei 1,0 = Referenzweiß</v>
+        <v>Lineare Werte</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>keine – Datei 1,0 = 1 cd/m²</v>
+        <v>Datei 1,0 = HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>Ziel-Spielraum</v>
+        <v>Datei 1,0 = 1 cd/m² (ICC.1 Abschnitt 8.10.2 a)</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
+        <v>OpenEXR- und Radiance-HDR-Dateien legen SDR-Weiß üblicherweise auf 1,0, während eine lineare ICC-Übertragung 1,0 als 1 cd/m² liest. Standardmäßig wird die Datei so skaliert, dass ihre 1,0 auf dem HDR-Referenzweiß des Profils liegt.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>Tone-Mapping</v>
+        <v>Eingangsskalierung</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>Auto (Rangfolge nach 8.10.3)</v>
+        <v>×{w} – Datei 1,0 = Referenzweiß</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>Verstärkungskurve (HAGC)</v>
+        <v>keine – Datei 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
+        <v>Ziel-Spielraum</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>Aus – wie ein CMM vor der Änderung</v>
+        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>Profil wird angewendet…</v>
+        <v>Tone-Mapping</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
+        <v>Auto (Rangfolge nach 8.10.3)</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
+        <v>Verstärkungskurve (HAGC)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
+        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>HDR-Profile</v>
+        <v>Aus – wie ein CMM vor der Änderung</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>Lineare Übertragung</v>
+        <v>Profil wird angewendet…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>Nichtlineare Übertragung (PQ, HLG)</v>
+        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR-Profile – lineare Übertragung</v>
+        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
+        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
+        <v>HDR-Profile</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
+        <v>Lineare Übertragung</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
+        <v>Nichtlineare Übertragung (PQ, HLG)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>HDR-Profile – lineare Übertragung</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Display-Spielraum</v>
+        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>Basis</v>
+        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Vorschau durch das Farbmodul</v>
+        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Tonemapping für {h} Blenden</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>Referenzweiß</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>Display-Spitze</v>
+        <v>Vorschau durch das Farbmodul</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>Vorschau nicht verfügbar: {why}</v>
+        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
+        <v>Tonemapping für {h} Blenden</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>Verstärkung über alle Headrooms</v>
+        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
+        <v>Referenzweiß</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>Display-Headroom (Blenden)</v>
+        <v>Vorschau nicht verfügbar: {why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>Verstärkung (Blenden)</v>
+        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>Kurve im Tag</v>
+        <v>Verstärkung über alle Headrooms</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>Basis</v>
+        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>Regler</v>
+        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>Eingang = Display-Spitze</v>
+        <v>Display-Headroom (Blenden)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Graue Tonkurven nach Headroom</v>
+        <v>Verstärkung (Blenden)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
+        <v>Kurve im Tag</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} Blenden</v>
+        <v>Regler</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} Blenden (Basis)</v>
+        <v>Eingang = Display-Spitze</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>Bei {h} Blenden (Regler)</v>
+        <v>Graue Tonkurven nach Headroom</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>{h} Blenden</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>{h} Blenden (Basis)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Bei {h} Blenden (Regler)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>Keine Änderung</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Displays erkennen</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>Vollbereich</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>BERICHT</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>Prüfungen</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>Abonnieren</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>Schließen</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>sie@example.com</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>(optional)</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>Abbrechen</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>Abonnieren</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>Schließen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>Fehler:</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>In XML konvertieren</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>ICC-Profil laden</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>Profil-ID</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>Tag-Name</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>Offset</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>Größe</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>Auffüllung</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>Typ</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>Array von {type}</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>Bytes</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>Profil ist gültig</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>Gültig</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>Warnung</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>Fehler</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>Unbekannt</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>Bestanden</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>Validierungsdetail</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>Feld</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>Aktueller Wert</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>Ungültig</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>Schließen</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>Einrückung</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (auch Gain-Map-JPEG), PNG – und HEIC in Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (auch Gain-Map-JPEG), PNG – und HEIC und JPEG XL in Safari.</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
+        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und geöffnet; heruntergeladen wird erst, wenn Sie auf „ICC-Profil speichern“ klicken.</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,4861 +1197,4869 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Nach Namen sortieren</v>
+        <v>Zum Auswählen tippen, dann auf einen Tab tippen zum Senden.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Nach Namen sortieren</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Neues Profil aus .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und geöffnet; heruntergeladen wird erst, wenn Sie auf „ICC-Profil speichern“ klicken.</v>
+        <v>Neues Profil aus .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>.cube-Datei wählen</v>
+        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und geöffnet; heruntergeladen wird erst, wenn Sie auf „ICC-Profil speichern“ klicken.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>.cube-Datei wählen</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>oder hierher ziehen oder unten einfügen</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Abbrechen</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Wird erstellt…</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profil</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Vergleichen</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Verknüpfen</v>
+        <v>Vergleichen</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spektral</v>
+        <v>Verknüpfen</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Entfernen</v>
+        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Kein Profil ausgewählt</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
+        <v>Kein Profil ausgewählt</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Noch nichts zu vergleichen</v>
+        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
+        <v>Noch nichts zu vergleichen</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Gamut-Vergleich</v>
+        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
+        <v>Gamut-Vergleich</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Render-Intent</v>
+        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Hülle</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Drahtgitter</v>
+        <v>Hülle</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Achsenwerte</v>
+        <v>Drahtgitter</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Deckkraft</v>
+        <v>Achsenwerte</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Farbe</v>
+        <v>Deckkraft</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Einfarbig</v>
+        <v>Farbe</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Nach Wert</v>
+        <v>Einfarbig</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Nach Farbton</v>
+        <v>Nach Wert</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotation</v>
+        <v>Nach Farbton</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Drehteller</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Orbit</v>
+        <v>Drehteller</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Ziehgeschwindigkeit</v>
+        <v>Orbit</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rollen</v>
+        <v>Ziehgeschwindigkeit</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Rollgeschwindigkeit</v>
+        <v>Rollen</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Gamut wird erstellt…</v>
+        <v>Rollgeschwindigkeit</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>kein Gamut</v>
+        <v>Gamut wird erstellt…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Ein-/ausblenden</v>
+        <v>kein Gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D-Gamut-Hülle</v>
+        <v>Ein-/ausblenden</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D-Gamut-Schnitt</v>
+        <v>3D-Gamut-Hülle</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Ebene</v>
+        <v>2D-Gamut-Schnitt</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Ebene</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Verknüpfung</v>
+        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
+        <v>Verknüpfung</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
+        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4-Display-Ersteller</v>
+        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
+        <v>V4-Display-Ersteller</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5-RGB-Display</v>
+        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>Displayprofil ablegen</v>
+        <v>V5-RGB-Display</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5-Beobachter (PCC)</v>
+        <v>Displayprofil ablegen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>Beobachterprofil ablegen</v>
+        <v>V5-Beobachter (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
+        <v>Beobachterprofil ablegen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>V4-Displayprofil erstellen</v>
+        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Profilname</v>
+        <v>V4-Displayprofil erstellen</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Erstellen</v>
+        <v>Profilname</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Wird erstellt…</v>
+        <v>Erstellen</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Link-Pipeline</v>
+        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
+        <v>Link-Pipeline</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Fertig</v>
+        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
+        <v>Fertig</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Bild wird geprüft…</v>
+        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
+        <v>Bild wird geprüft…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
+        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Bild transformieren</v>
+        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Wird transformiert…</v>
+        <v>Bild transformieren</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Profile ablegen, um die Kette zu starten</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>entfernt</v>
+        <v>Profile ablegen, um die Kette zu starten</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Nach vorne verschieben</v>
+        <v>entfernt</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Nach hinten verschieben</v>
+        <v>Nach vorne verschieben</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Nach oben verschieben</v>
+        <v>Nach hinten verschieben</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Nach unten verschieben</v>
+        <v>Nach oben verschieben</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Rendering-Priorität (alle)</v>
+        <v>Nach unten verschieben</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Rendering-Priorität für diese Transformation</v>
+        <v>Rendering-Priorität (alle)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
+        <v>Rendering-Priorität für diese Transformation</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
+        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
+        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Kette</v>
+        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Die Kette konnte nicht analysiert werden.</v>
+        <v>Kette</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Kette wird geprüft…</v>
+        <v>Die Kette konnte nicht analysiert werden.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>Die Kette verbindet sich nicht ({detail}).</v>
+        <v>Kette wird geprüft…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
+        <v>Die Kette verbindet sich nicht ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
+        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Leeren</v>
+        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink-Name</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Wird erstellt…</v>
+        <v>DeviceLink-Name</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
+        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
+        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
+        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformiertes Bild gespeichert.</v>
+        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformiertes Bild gespeichert.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Datendatei zu groß.</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Daten transformieren</v>
+        <v>Datendatei zu groß.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Wird transformiert…</v>
+        <v>Daten transformieren</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Bevorzugen</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Beobachter</v>
+        <v>Bevorzugen</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Lichtart</v>
+        <v>Beobachter</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Bedingung</v>
+        <v>Lichtart</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} Duplikat(e) filtern</v>
+        <v>Bedingung</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>Median</v>
+        <v>{n} Duplikat(e) filtern</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>Mittelwert</v>
+        <v>Median</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>Farbfelder</v>
+        <v>Mittelwert</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} Duplikate</v>
+        <v>Farbfelder</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Transformationsergebnis</v>
+        <v>{n} Duplikate</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} Farbfelder</v>
+        <v>Transformationsergebnis</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
+        <v>{src} → {dst} · {n} Farbfelder</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Speichern unter</v>
+        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Speichern</v>
+        <v>Speichern unter</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Transformation umkehren</v>
+        <v>Speichern</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Wird umgekehrt…</v>
+        <v>Transformation umkehren</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Umkehren</v>
+        <v>Wird umgekehrt…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>letzte Stufe</v>
+        <v>Umkehren</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>erste Stufe</v>
+        <v>letzte Stufe</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Daten in {in} → Suche {out}</v>
+        <v>erste Stufe</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
+        <v>Daten in {in} → Suche {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
+        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE-Kosten</v>
+        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
+        <v>ΔE-Kosten</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extrahieren &amp; zur Kette hinzufügen</v>
+        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Wird extrahiert…</v>
+        <v>Extrahieren &amp; zur Kette hinzufügen</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Verwerfen</v>
+        <v>Wird extrahiert…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
+        <v>Verwerfen</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Bildausgabeoptionen</v>
+        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Kodierung</v>
+        <v>Bildausgabeoptionen</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Wie Quelle</v>
+        <v>Kodierung</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 Bit</v>
+        <v>Wie Quelle</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 Bit</v>
+        <v>8 Bit</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Gleitkomma (32 Bit)</v>
+        <v>16 Bit</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Komprimierung</v>
+        <v>Gleitkomma (32 Bit)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Keine</v>
+        <v>Komprimierung</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planar</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Verschachtelt</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Getrennt</v>
+        <v>Verschachtelt</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM-Interpolation</v>
+        <v>Getrennt</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraedrisch</v>
+        <v>CMM-Interpolation</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linear</v>
+        <v>Tetraedrisch</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>ICC-Profil einbetten</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
+        <v>ICC-Profil einbetten</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Spektrales TIFF zusammenstellen</v>
+        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
+        <v>Spektrales TIFF zusammenstellen</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
+        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>Kan</v>
+        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Zusammenfügen &amp; Speichern</v>
+        <v>Kan</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Wird zusammengefügt…</v>
+        <v>Zusammenfügen &amp; Speichern</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n} Kanäle zusammengefügt.</v>
+        <v>Wird zusammengefügt…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
+        <v>{n} Kanäle zusammengefügt.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Abbrechen</v>
+        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} Datei(en) nicht geladen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
+        <v>{n} Datei(en) nicht geladen</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>oder</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Datei wählen</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Header</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validierung</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analyse</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Render-Intent</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% Farbe</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* Ausgabe (Tonwert)</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* Ausgabe (Tonwert)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Kolorimetrie der Extremwerte</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Die Enden des Wiedergabeumfangs des Profils: das Weiß des Bedruckstoffs, das dunkelste Schwarz, das es druckt, der Farbauftrag, den dieses Schwarz kostet, und der Punkt, an dem jeder Farbton am gesättigtsten ist.</v>
+        <v>Kolorimetrie der Extremwerte</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Der Weißpunkt ist die Farbe bei null Farbmittel — der blanke Bedruckstoff. Der Schwarzpunkt ergibt sich, indem PCS-Schwarz (L*=0, a*=b*=0) durch die gewählte B2A-Tabelle geführt wird, um den Farbauftrag zu erhalten, den das Profil für Schwarz wählt, und dieser Farbauftrag anschließend über A2B1 zurückgelesen wird. Der Gesamtfarbauftrag (TAC) ist die Summe dieses Farbauftrags. Die absolute Kolorimetrie zeigt die Eigenfarbe des Bedruckstoffs; die relative bezieht sie auf ein perfektes Weiß.</v>
+        <v>Die Enden des Wiedergabeumfangs des Profils: das Weiß des Bedruckstoffs, das dunkelste Schwarz, das es druckt, der Farbauftrag, den dieses Schwarz kostet, und der Punkt, an dem jeder Farbton am gesättigtsten ist.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativ</v>
+        <v>Der Weißpunkt ist die Farbe bei null Farbmittel — der blanke Bedruckstoff. Der Schwarzpunkt ergibt sich, indem PCS-Schwarz (L*=0, a*=b*=0) durch die gewählte B2A-Tabelle geführt wird, um den Farbauftrag zu erhalten, den das Profil für Schwarz wählt, und dieser Farbauftrag anschließend über A2B1 zurückgelesen wird. Der Gesamtfarbauftrag (TAC) ist die Summe dieses Farbauftrags. Die absolute Kolorimetrie zeigt die Eigenfarbe des Bedruckstoffs; die relative bezieht sie auf ein perfektes Weiß.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absolut</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Weißpunkt</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Schwarzpunkt</v>
+        <v>Weißpunkt</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Farbauftrag am Schwarzpunkt</v>
+        <v>Schwarzpunkt</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Farbauftrag am Schwarzpunkt</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Dieses Profil hat kein Medien-Weißpunkt-Tag, daher ist die absolute Kolorimetrie nicht verfügbar.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>Die Kolorimetrie der Extremwerte ist nur für Ausgabeprofile (Drucker) verfügbar — sie setzt voraus, dass null Farbmittel dem blanken Bedruckstoff entspricht.</v>
+        <v>Dieses Profil hat kein Medien-Weißpunkt-Tag, daher ist die absolute Kolorimetrie nicht verfügbar.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Vollton gegenüber maximalem Chroma</v>
+        <v>Die Kolorimetrie der Extremwerte ist nur für Ausgabeprofile (Drucker) verfügbar — sie setzt voraus, dass null Farbmittel dem blanken Bedruckstoff entspricht.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Wo jede Farbecke landet und der farbigste Punkt auf dem Weg dorthin. Gemessen über A2B1, daher ändern sich diese Zeilen nicht mit dem Render-Intent oben. Bei einem gutmütigen Profil stimmen beide Zeilen überein; wird das maximale Chroma vor dem Vollton erreicht, verdunkelt die Farbe darüber hinaus nur noch.</v>
+        <v>Vollton gegenüber maximalem Chroma</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Farbton</v>
+        <v>Wo jede Farbecke landet und der farbigste Punkt auf dem Weg dorthin. Gemessen über A2B1, daher ändern sich diese Zeilen nicht mit dem Render-Intent oben. Bei einem gutmütigen Profil stimmen beide Zeilen überein; wird das maximale Chroma vor dem Vollton erreicht, verdunkelt die Farbe darüber hinaus nur noch.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Vollton</v>
+        <v>Farbton</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>Max. C*</v>
+        <v>Vollton</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Bei Farbauftrag</v>
+        <v>Max. C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>Das maximale Chroma wird vor dem Vollton erreicht — Farbe darüber hinaus verdunkelt nur.</v>
+        <v>Bei Farbauftrag</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Farbverbrauch in den Tiefen</v>
+        <v>Das maximale Chroma wird vor dem Vollton erreicht — Farbe darüber hinaus verdunkelt nur.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Vier gerade Pfade durch die a*b*-Ebene bei einer konstanten, bewusst dunklen Helligkeit, geführt durch die gewählte B2A-Tabelle. Alle Abtastwerte teilen dieselbe L*, sodass jeder abrupte Sprung oder jede Umkehr eines Farbmittels allein aus der Behandlung von Farbton und Chroma stammt — die Signatur eines Gamut-Mapping-Artefakts in den Tiefen.</v>
+        <v>Farbverbrauch in den Tiefen</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>Der Farbverbrauch in den Tiefen ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Vier gerade Pfade durch die a*b*-Ebene bei einer konstanten, bewusst dunklen Helligkeit, geführt durch die gewählte B2A-Tabelle. Alle Abtastwerte teilen dieselbe L*, sodass jeder abrupte Sprung oder jede Umkehr eines Farbmittels allein aus der Behandlung von Farbton und Chroma stammt — die Signatur eines Gamut-Mapping-Artefakts in den Tiefen.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Ebene konstanter L*</v>
+        <v>Der Farbverbrauch in den Tiefen ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>schwarzpunktkompensiert ab</v>
+        <v>Ebene konstanter L*</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Position entlang des Pfades</v>
+        <v>schwarzpunktkompensiert ab</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Pfad</v>
+        <v>Position entlang des Pfades</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Primärfarben-Pfade durch Neutral</v>
+        <v>Pfad</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Drei Pfade im Gamut — Cyan→Rot, Magenta→Grün, Gelb→Blau — jeder durch die Neutralachse bei der mittleren Helligkeit seiner Endpunkte, durch die gewählte B2A-Tabelle geführt. Jeder Messpunkt liegt im Gamut, daher ist – anders als bei den Schattenpfaden – jede abrupte Stufe oder Umkehr eines Farbmittels ein CLUT-Glättungsfehler und kein Gamut-Mapping-Artefakt.</v>
+        <v>Primärfarben-Pfade durch Neutral</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Primärfarben-Pfade sind nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Drei Pfade im Gamut — Cyan→Rot, Magenta→Grün, Gelb→Blau — jeder durch die Neutralachse bei der mittleren Helligkeit seiner Endpunkte, durch die gewählte B2A-Tabelle geführt. Jeder Messpunkt liegt im Gamut, daher ist – anders als bei den Schattenpfaden – jede abrupte Stufe oder Umkehr eines Farbmittels ein CLUT-Glättungsfehler und kein Gamut-Mapping-Artefakt.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Position entlang des Pfades (Neutral in der Mitte)</v>
+        <v>Primärfarben-Pfade sind nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Schwarzpunktkompensation für diese Absicht angewendet.</v>
+        <v>Position entlang des Pfades (Neutral in der Mitte)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Farbverbrauchsstatistik</v>
+        <v>Schwarzpunktkompensation für diese Absicht angewendet.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Wie viel von jedem Farbmittel das Profil aufträgt, als Summe und als Anteil am Gesamtwert — die Farbverbrauchssignatur der Separation.</v>
+        <v>Farbverbrauchsstatistik</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Die Farbverbrauchsstatistik ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Wie viel von jedem Farbmittel das Profil aufträgt, als Summe und als Anteil am Gesamtwert — die Farbverbrauchssignatur der Separation.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Neutralachse</v>
+        <v>Die Farbverbrauchsstatistik ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Mittlere Deckung</v>
+        <v>Neutralachse</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Farbanteil</v>
+        <v>Mittlere Deckung</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>Der Farbanteil ist der Fingerabdruck des Neutralaufbaus — der Anteil jedes Farbmittels an der gesamten aufgetragenen Farbe, unabhängig von der Anzahl der Messpunkte.</v>
+        <v>Farbanteil</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Punkte im Gamut</v>
+        <v>Der Farbanteil ist der Fingerabdruck des Neutralaufbaus — der Anteil jedes Farbmittels an der gesamten aufgetragenen Farbe, unabhängig von der Anzahl der Messpunkte.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>Der Farbverbrauch über alle Gamut-Farben benötigt die B2A-Gamutgrenze, die noch nicht implementiert ist — ausstehend.</v>
+        <v>Punkte im Gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Keine Farbmitteldaten zum Zusammenfassen.</v>
+        <v>Der Farbverbrauch über alle Gamut-Farben benötigt die B2A-Gamutgrenze, die noch nicht implementiert ist — ausstehend.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Wählen Sie unten eine B2A-Tabelle (PCS→Gerät), um auch ein Graustufenbild der Farbdeckung für jedes Farbmittel anzuzeigen.</v>
+        <v>Keine Farbmitteldaten zum Zusammenfassen.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Farbdeckung jedes Farbmittels über dasselbe Gitter (dunkler = mehr Farbe).</v>
+        <v>Wählen Sie unten eine B2A-Tabelle (PCS→Gerät), um auch ein Graustufenbild der Farbdeckung für jedes Farbmittel anzuzeigen.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cyan</v>
+        <v>Farbdeckung jedes Farbmittels über dasselbe Gitter (dunkler = mehr Farbe).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Gelb</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rot</v>
+        <v>Gelb</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Grün</v>
+        <v>Rot</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Blau</v>
+        <v>Grün</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Schwarz</v>
+        <v>Blau</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perzeptiv</v>
+        <v>Schwarz</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Sättigung</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Profilstatistik</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Render-Intent</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>Mittel</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>Max.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analyse läuft…</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analyse</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Diagramm</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Rohausgabe</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Kurven</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Eingangskurven</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Ausgangskurven</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT-Bild</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Gamut-Bild</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Chromazität</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Streudiagramm</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Tonwertkurve</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Kurventabelle</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabellen</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Daten</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Auswerten</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Wird geladen…</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Eingang</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Ausgang</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Gleitkomma</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Gitterpunkt</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalisiert</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Lesbar</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Gerät → PCS</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Gerät</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Wird geladen…</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Sicherheit</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Konformität</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualität</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>Codepunkte</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>Verstärkungskurve</v>
+        <v>Codepunkte</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>Umgebung</v>
+        <v>Verstärkungskurve</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>SDR-Rückfall wird angezeigt</v>
+        <v>Umgebung</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>HDR-Profil in der Kette</v>
+        <v>SDR-Rückfall wird angezeigt</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Transformationen über ein HDR-Profil nutzen dessen AToB0Tag — das von Abschnitt 8.10.6 geforderte feste SDR-Rendering — da Abschnitt 8.10.1 keine TRC-Tags zulässt. Das Ergebnis ist dieser Rückfall, kein HDR-Verhalten.</v>
+        <v>HDR-Profil in der Kette</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Dies sind HDR-Profile ohne TRC-Tags; der Gamut wird daher aus dem AToB0Tag gebildet — dem festen SDR-Rendering, das Abschnitt 8.10.6 für Anwendungen ohne HDR-Verarbeitung verlangt. Es ist nicht der HDR-Gamut des Profils, der in einem begrenzten PCS nicht darstellbar ist.</v>
+        <v>Transformationen über ein HDR-Profil nutzen dessen AToB0Tag — das von Abschnitt 8.10.6 geforderte feste SDR-Rendering — da Abschnitt 8.10.1 keine TRC-Tags zulässt. Das Ergebnis ist dieser Rückfall, kein HDR-Verhalten.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Erkennung…</v>
+        <v>Dies sind HDR-Profile ohne TRC-Tags; der Gamut wird daher aus dem AToB0Tag gebildet — dem festen SDR-Rendering, das Abschnitt 8.10.6 für Anwendungen ohne HDR-Verarbeitung verlangt. Es ist nicht der HDR-Gamut des Profils, der in einem begrenzten PCS nicht darstellbar ist.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>Umgebung konnte nicht erkannt werden.</v>
+        <v>Erkennung…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>HDR-Display</v>
+        <v>Umgebung konnte nicht erkannt werden.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>Erweiterter Gamut</v>
+        <v>HDR-Display</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>HDR-Canvas-Pfad</v>
+        <v>Erweiterter Gamut</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>HDR-Canvas-Pfad</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>keiner</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>ja</v>
+        <v>keiner</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>nein</v>
+        <v>ja</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>nicht gemeldet</v>
+        <v>nein</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>Format</v>
+        <v>nicht gemeldet</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>Prüfen</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>Anzeigen</v>
+        <v>Prüfen</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>Anzeigen</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>Eingebettetes ICC-Profil lesen — kein Codec nötig</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>Pixel anzeigen</v>
+        <v>Eingebettetes ICC-Profil lesen — kein Codec nötig</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>Heller als Weiß darstellen</v>
+        <v>Pixel anzeigen</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>Von profiletool selbst dekodiert, also browserunabhängig</v>
+        <v>Heller als Weiß darstellen</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>Dieser Browser hat den HDR-Spielraum des Displays nicht gemeldet, nur ob ein HDR-Pfad existiert.</v>
+        <v>Von profiletool selbst dekodiert, also browserunabhängig</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>Browser-Flags</v>
+        <v>Dieser Browser hat den HDR-Spielraum des Displays nicht gemeldet, nur ob ein HDR-Pfad existiert.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>aktiv</v>
+        <v>Browser-Flags</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>nicht aktiviert</v>
+        <v>aktiv</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>hier nicht erkennbar</v>
+        <v>nicht aktiviert</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>Für HDR-Darstellung in diesem Browser nötig: ohne WebGPU ist das HDR-Canvas der einzige Weg. Die Profilprüfung funktioniert auch ohne.</v>
+        <v>hier nicht erkennbar</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>Optional: HDR kann über WebGPU dargestellt werden, dies ergänzt aber den HDR-Canvas-Weg und lässt profiletool den echten HDR-Spielraum des Bildschirms lesen.</v>
+        <v>Für HDR-Darstellung in diesem Browser nötig: ohne WebGPU ist das HDR-Canvas der einzige Weg. Die Profilprüfung funktioniert auch ohne.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>Webseiten können keine Flag-Seiten öffnen. Fügen Sie dies in die Adressleiste ein, stellen Sie Enabled ein und starten Sie den Browser neu.</v>
+        <v>Optional: HDR kann über WebGPU dargestellt werden, dies ergänzt aber den HDR-Canvas-Weg und lässt profiletool den echten HDR-Spielraum des Bildschirms lesen.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>Kopieren</v>
+        <v>Webseiten können keine Flag-Seiten öffnen. Fügen Sie dies in die Adressleiste ein, stellen Sie Enabled ein und starten Sie den Browser neu.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>Kopiert</v>
+        <v>Kopieren</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>Kopieren fehlgeschlagen — Adresse markieren und kopieren.</v>
+        <v>Kopiert</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>Pixelverhältnis</v>
+        <v>Kopieren fehlgeschlagen — Adresse markieren und kopieren.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>Aktueller Monitor</v>
+        <v>Pixelverhältnis</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>ohne Namen</v>
+        <v>Aktueller Monitor</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>primär</v>
+        <v>ohne Namen</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>eingebaut</v>
+        <v>primär</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>HDR-Spielraum</v>
+        <v>eingebaut</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>von diesem Browser nicht bereitgestellt</v>
+        <v>HDR-Spielraum</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium meldet dies in Blendenstufen: log₂ aus Spitzenhelligkeit des Displays ÷ SDR-Weißpegel. Unter Windows wird der Wert nur aktualisiert, wenn Chrome das Display neu einliest – Fenster auf einen anderen Bildschirm verschoben oder Chrome wieder aktiviert –, nicht bei Helligkeitsänderungen.</v>
+        <v>von diesem Browser nicht bereitgestellt</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} Blendenstufen (≈{ratio}× SDR-Weiß)</v>
+        <v>Chromium meldet dies in Blendenstufen: log₂ aus Spitzenhelligkeit des Displays ÷ SDR-Weißpegel. Unter Windows wird der Wert nur aktualisiert, wenn Chrome das Display neu einliest – Fenster auf einen anderen Bildschirm verschoben oder Chrome wieder aktiviert –, nicht bei Helligkeitsänderungen.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} Blendenstufen (≈{ratio}× SDR-Weiß)</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>Verstärkung bei einem Display-Spielraum</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>Ein HDR-Bild auf diesem Display ansehen. Dateien, die der Browser dekodieren kann, zeigt der Browser selbst an; OpenEXR und Radiance HDR werden von profiletool dekodiert und dargestellt.</v>
+        <v>Verstärkung bei einem Display-Spielraum</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>HDR-Bild hier ablegen oder klicken, um eines auszuwählen</v>
+        <v>Ein HDR-Bild auf diesem Display ansehen. Dateien, die der Browser dekodieren kann, zeigt der Browser selbst an; OpenEXR und Radiance HDR werden von profiletool dekodiert und dargestellt.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (auch Gain-Map-JPEG), PNG – und HEIC und JPEG XL in Safari.</v>
+        <v>HDR-Bild hier ablegen oder klicken, um eines auszuwählen</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>Anderes wählen</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (auch Gain-Map-JPEG), PNG – und HEIC und JPEG XL in Safari.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>Leeren</v>
+        <v>Anderes wählen</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>Eingebettetes ICC-Profil</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>keins – OpenEXR gibt Farbe über Chromatizitäten an</v>
+        <v>Eingebettetes ICC-Profil</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>keins – Radiance HDR gibt Farbe über seine PRIMARIES-Kopfzeile an</v>
+        <v>keins – OpenEXR gibt Farbe über Chromatizitäten an</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>wird geprüft…</v>
+        <v>keins – Radiance HDR gibt Farbe über seine PRIMARIES-Kopfzeile an</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>keins</v>
+        <v>wird geprüft…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>Im Tab „Profil“ öffnen</v>
+        <v>keins</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>Gain-Map</v>
+        <v>Im Tab „Profil“ öffnen</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>erkannt, nicht dekodiert</v>
+        <v>Gain-Map</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>Das ist kein Bild. Profile über den Profilbereich laden.</v>
+        <v>erkannt, nicht dekodiert</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>Kein Bildformat, das profiletool erkennt.</v>
+        <v>Das ist kein Bild. Profile über den Profilbereich laden.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>TIFF-Pixel werden hier noch nicht angezeigt: Browser dekodieren kein TIFF, und wie HDR in einem 16-Bit-TIFF kodiert wird, ist noch offen (Phase 4.3). Das eingebettete Profil kann untersucht werden.</v>
+        <v>Kein Bildformat, das profiletool erkennt.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>Dieses Bild kann hier nicht angezeigt werden:</v>
+        <v>TIFF-Pixel werden hier noch nicht angezeigt: Browser dekodieren kein TIFF, und wie HDR in einem 16-Bit-TIFF kodiert wird, ist noch offen (Phase 4.3). Das eingebettete Profil kann untersucht werden.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>Das eingebettete Profil kann trotzdem untersucht werden.</v>
+        <v>Dieses Bild kann hier nicht angezeigt werden:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>Angezeigt von</v>
+        <v>Das eingebettete Profil kann trotzdem untersucht werden.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>dem Browser</v>
+        <v>Angezeigt von</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>dem Browser</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>HDR-Display</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>Browser ignorieren HDR, das nur durch ein eingebettetes ICC-Profil angegeben ist; dieses Bild kann daher matt und flach wirken.</v>
+        <v>HDR-Display</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>Dieser Browser kann ein Bild nicht zwischen SDR und HDR umschalten; es wird so gezeigt, wie der Browser es darstellt.</v>
+        <v>Browser ignorieren HDR, das nur durch ein eingebettetes ICC-Profil angegeben ist; dieses Bild kann daher matt und flach wirken.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>Der Browser konnte dieses Bild nicht dekodieren.</v>
+        <v>Dieser Browser kann ein Bild nicht zwischen SDR und HDR umschalten; es wird so gezeigt, wie der Browser es darstellt.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>Ausgabe</v>
+        <v>Der Browser konnte dieses Bild nicht dekodieren.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>HDR-Canvas (float16)</v>
+        <v>Ausgabe</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU (erweiterter Bereich)</v>
+        <v>HDR-Canvas (float16)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>SDR-Canvas (Tone-Mapping)</v>
+        <v>WebGPU (erweiterter Bereich)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>Größe</v>
+        <v>SDR-Canvas (Tone-Mapping)</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>Hellstes Pixel</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>{n}× SDR-Weiß</v>
+        <v>Hellstes Pixel</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>Chromatizitäten</v>
+        <v>{n}× SDR-Weiß</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>nicht angegeben – Rec. 709 angenommen</v>
+        <v>Chromatizitäten</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from} ist hier nicht verfügbar ({why}); die nächste Ausgabe wird verwendet.</v>
+        <v>nicht angegeben – Rec. 709 angenommen</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>Diese Ausgabe kann keine Werte heller als Weiß transportieren; die SDR-Darstellung mit Tone-Mapping wird gezeigt.</v>
+        <v>{from} ist hier nicht verfügbar ({why}); die nächste Ausgabe wird verwendet.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>Belichtung</v>
+        <v>Diese Ausgabe kann keine Werte heller als Weiß transportieren; die SDR-Darstellung mit Tone-Mapping wird gezeigt.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} Blendenstufen</v>
+        <v>Belichtung</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>Dekodierung fehlgeschlagen:</v>
+        <v>{n} Blendenstufen</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>Diese Datei ist {size} MB groß; der HDR-Tab öffnet Bilder bis {max} MB.</v>
+        <v>Dekodierung fehlgeschlagen:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>Profil konnte nicht angewendet werden:</v>
+        <v>Diese Datei ist {size} MB groß; der HDR-Tab öffnet Bilder bis {max} MB.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>Bild konnte nicht gezeichnet werden:</v>
+        <v>Profil konnte nicht angewendet werden:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>(diese Primärfarben definieren keinen Farbraum – ignoriert, Rec. 709 verwendet)</v>
+        <v>Bild konnte nicht gezeichnet werden:</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>das Profil eines JPEG XL ist im Codestream komprimiert, den profiletool noch nicht dekomprimiert</v>
+        <v>(diese Primärfarben definieren keinen Farbraum – ignoriert, Rec. 709 verwendet)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>Wird dekodiert…</v>
+        <v>das Profil eines JPEG XL ist im Codestream komprimiert, den profiletool noch nicht dekomprimiert</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>Dynamikumfang</v>
+        <v>Wird dekodiert…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>Dieser Browser bietet nur die beiden Enden, keine Mischung.</v>
+        <v>Dynamikumfang</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>von profiletool selbst dekodiert, daher browserunabhängig</v>
+        <v>Dieser Browser bietet nur die beiden Enden, keine Mischung.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>dieser Browser dekodiert es</v>
+        <v>von profiletool selbst dekodiert, daher browserunabhängig</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>dieser Browser dekodiert es nicht</v>
+        <v>dieser Browser dekodiert es</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>HEIC-Anzeige erfordert Safari oder einen anderen WebKit-Browser – Chrome und Firefox dekodieren HEIC auf keiner Plattform, auch nicht unter macOS</v>
+        <v>dieser Browser dekodiert es nicht</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>JPEG-XL-Anzeige erfordert Safari; andere Browser unterstützen es noch nicht</v>
+        <v>HEIC-Anzeige erfordert Safari oder einen anderen WebKit-Browser – Chrome und Firefox dekodieren HEIC auf keiner Plattform, auch nicht unter macOS</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>auf eine spätere Version verschoben</v>
+        <v>JPEG-XL-Anzeige erfordert Safari; andere Browser unterstützen es noch nicht</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>dieses Display meldet keinen HDR-Pfad, daher wird HDR per Tone-Mapping als SDR dargestellt</v>
+        <v>auf eine spätere Version verschoben</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>dieser Browser bietet keinen HDR-Canvas-Pfad (float16-Canvas oder WebGPU nötig)</v>
+        <v>dieses Display meldet keinen HDR-Pfad, daher wird HDR per Tone-Mapping als SDR dargestellt</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox zeigt keine HDR-Bilder und liest keine Gain-Maps; HDR-Inhalte werden als SDR gezeigt</v>
+        <v>dieser Browser bietet keinen HDR-Canvas-Pfad (float16-Canvas oder WebGPU nötig)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>die Untersuchung braucht nur das Parsen des Containers, keinen Codec</v>
+        <v>Firefox zeigt keine HDR-Bilder und liest keine Gain-Maps; HDR-Inhalte werden als SDR gezeigt</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>HDR-Display und HDR-Canvas-Pfad sind beide verfügbar</v>
+        <v>die Untersuchung braucht nur das Parsen des Containers, keinen Codec</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>unbekanntes Format</v>
+        <v>HDR-Display und HDR-Canvas-Pfad sind beide verfügbar</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{browser} unter {os}</v>
+        <v>unbekanntes Format</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · HDR-Display erkannt</v>
+        <v>{browser} unter {os}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · SDR-Display</v>
+        <v>{name} · HDR-Display erkannt</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU hat Tone-Mapping „{mode}“ angewendet; die Ausgabe ist daher auf SDR begrenzt</v>
+        <v>{name} · SDR-Display</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>Dieser Browser meldet das angewendete WebGPU-Tone-Mapping nicht; HDR-Ausgabe ist unbestätigt</v>
+        <v>WebGPU hat Tone-Mapping „{mode}“ angewendet; die Ausgabe ist daher auf SDR begrenzt</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>Display-Spitze</v>
+        <v>Dieser Browser meldet das angewendete WebGPU-Tone-Mapping nicht; HDR-Ausgabe ist unbestätigt</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>{r}× SDR-Weiß ({n} Blendenstufen)</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× – SDR-Display</v>
+        <v>{r}× SDR-Weiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>unbekannt</v>
+        <v>1× – SDR-Display</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>Dieses Display meldet kein HDR, daher zeigt der Browser das Bild an beiden Enden als SDR.</v>
+        <v>unbekannt</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>Dieses Display meldet kein HDR, daher wird alles heller als SDR-Weiß abgeschnitten. „An Display anpassen“ zeigt stattdessen die Darstellung mit Tone-Mapping.</v>
+        <v>Dieses Display meldet kein HDR, daher zeigt der Browser das Bild an beiden Enden als SDR.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>Dieses Bild verlangt {img}× SDR-Weiß, dieses Display zeigt aber nur bis {disp}×; hellere Werte werden abgeschnitten. „An Display anpassen“ lässt sie stattdessen sanft in die Display-Spitze auslaufen.</v>
+        <v>Dieses Display meldet kein HDR, daher wird alles heller als SDR-Weiß abgeschnitten. „An Display anpassen“ zeigt stattdessen die Darstellung mit Tone-Mapping.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>An Display anpassen</v>
+        <v>Dieses Bild verlangt {img}× SDR-Weiß, dieses Display zeigt aber nur bis {disp}×; hellere Werte werden abgeschnitten. „An Display anpassen“ lässt sie stattdessen sanft in die Display-Spitze auslaufen.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>Bilddetails</v>
+        <v>An Display anpassen</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>nicht verfügbar – der Browser stellt dieses Bild dar und kann es nicht auf eine feste Spitze begrenzen</v>
+        <v>Bilddetails</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>nicht verfügbar – diese Ausgabe zeigt nichts über SDR-Weiß</v>
+        <v>nicht verfügbar – der Browser stellt dieses Bild dar und kann es nicht auf eine feste Spitze begrenzen</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>nicht verfügbar – die Spitzenhelligkeit dieses Displays ist unbekannt</v>
+        <v>nicht verfügbar – diese Ausgabe zeigt nichts über SDR-Weiß</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>Vergrößern</v>
+        <v>nicht verfügbar – die Spitzenhelligkeit dieses Displays ist unbekannt</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>Verkleinern</v>
+        <v>Vergrößern</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>Bild einpassen</v>
+        <v>Verkleinern</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>Echte Pixel (1:1)</v>
+        <v>Bild einpassen</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>Ziehen zum Verschieben · Strg+Mausrad zum Zoomen · Doppelklick zum Zurücksetzen</v>
+        <v>Echte Pixel (1:1)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>Ziehen, um den Bildbereich zu ändern; Doppelklick stellt die Standardgröße wieder her</v>
+        <v>Ziehen zum Verschieben · Strg+Mausrad zum Zoomen · Doppelklick zum Zurücksetzen</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>Bildansicht</v>
+        <v>Ziehen, um den Bildbereich zu ändern; Doppelklick stellt die Standardgröße wieder her</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
+        <v>Bildansicht</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>keine Grenze</v>
+        <v>Begrenzt die Helligkeit auf die Spitze, die dieses Display meldet. Unter Windows kann dieser Wert Helligkeitsänderungen hinterherhinken.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>Grenze {n} Blendenstufen ({r}×)</v>
+        <v>keine Grenze</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>SDR-Weiß</v>
+        <v>Grenze {n} Blendenstufen ({r}×)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
+        <v>SDR-Weiß</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>SDR-Weiß-Feld</v>
+        <v>Einfaches SDR-Weiß zum Vergleich. Auf einem HDR-Display wirken HDR-Spitzlichter heller als dieses.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
+        <v>SDR-Weiß-Feld</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>Profil zuweisen</v>
+        <v>Zum Verschieben ziehen; Doppelklick setzt es wieder neben das Bild.</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>Keins – was die Datei angibt</v>
+        <v>Profil zuweisen</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>Eingebettetes Profil ({n} B)</v>
+        <v>Keins – was die Datei angibt</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR-Profile im Pool</v>
+        <v>Eingebettetes Profil ({n} B)</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>Profil</v>
+        <v>HDR-Profile im Pool</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>eingebettetes Profil</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>Pfad des Farbmoduls</v>
+        <v>eingebettetes Profil</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
+        <v>Pfad des Farbmoduls</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>HDR-Pfad, keine Verstärkungskurve</v>
+        <v>HDR-Pfad, Verstärkungskurve angewendet</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
+        <v>HDR-Pfad, keine Verstärkungskurve</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>Übertragung</v>
+        <v>Vorberechnetes AToB0 – nicht der HDR-Pfad</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR-Referenzweiß</v>
+        <v>Übertragung</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Lineare Werte</v>
+        <v>HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>Datei 1,0 = HDR-Referenzweiß</v>
+        <v>Lineare Werte</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>Datei 1,0 = 1 cd/m² (ICC.1 Abschnitt 8.10.2 a)</v>
+        <v>Datei 1,0 = HDR-Referenzweiß</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>OpenEXR- und Radiance-HDR-Dateien legen SDR-Weiß üblicherweise auf 1,0, während eine lineare ICC-Übertragung 1,0 als 1 cd/m² liest. Standardmäßig wird die Datei so skaliert, dass ihre 1,0 auf dem HDR-Referenzweiß des Profils liegt.</v>
+        <v>Datei 1,0 = 1 cd/m² (ICC.1 Abschnitt 8.10.2 a)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>Eingangsskalierung</v>
+        <v>OpenEXR- und Radiance-HDR-Dateien legen SDR-Weiß üblicherweise auf 1,0, während eine lineare ICC-Übertragung 1,0 als 1 cd/m² liest. Standardmäßig wird die Datei so skaliert, dass ihre 1,0 auf dem HDR-Referenzweiß des Profils liegt.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} – Datei 1,0 = Referenzweiß</v>
+        <v>Eingangsskalierung</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>keine – Datei 1,0 = 1 cd/m²</v>
+        <v>×{w} – Datei 1,0 = Referenzweiß</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>Ziel-Spielraum</v>
+        <v>keine – Datei 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
+        <v>Ziel-Spielraum</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Tone-Mapping</v>
+        <v>{r}× Referenzweiß ({n} Blendenstufen)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>Auto (Rangfolge nach 8.10.3)</v>
+        <v>Tone-Mapping</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Verstärkungskurve (HAGC)</v>
+        <v>Auto (Rangfolge nach 8.10.3)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
+        <v>Verstärkungskurve (HAGC)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>Aus – wie ein CMM vor der Änderung</v>
+        <v>Vorberechneter SDR-Ersatz (AToB0)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>Profil wird angewendet…</v>
+        <v>Aus – wie ein CMM vor der Änderung</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
+        <v>Profil wird angewendet…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
+        <v>{format} enthält lineares Licht und braucht daher ein Profil mit Übertragung Linear (8).</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
+        <v>Ein Profil zuzuweisen erfordert ein RGB-Bild mit 3 Kanälen.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>HDR-Profile</v>
+        <v>Um seine Werte zu interpretieren, oben ein Profil zuweisen.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Lineare Übertragung</v>
+        <v>HDR-Profile</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>Nichtlineare Übertragung (PQ, HLG)</v>
+        <v>Lineare Übertragung</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>HDR-Profile – lineare Übertragung</v>
+        <v>Nichtlineare Übertragung (PQ, HLG)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
+        <v>HDR-Profile – lineare Übertragung</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
+        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
+        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
+        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>Display-Spielraum</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>Basis</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>Vorschau durch das Farbmodul</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
+        <v>Vorschau durch das Farbmodul</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>Tonemapping für {h} Blenden</v>
+        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
+        <v>Tonemapping für {h} Blenden</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>Referenzweiß</v>
+        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>Display-Spitze</v>
+        <v>Referenzweiß</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>Vorschau nicht verfügbar: {why}</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
+        <v>Vorschau nicht verfügbar: {why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>Verstärkung über alle Headrooms</v>
+        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
+        <v>Verstärkung über alle Headrooms</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>Display-Headroom (Blenden)</v>
+        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Verstärkung (Blenden)</v>
+        <v>Display-Headroom (Blenden)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Kurve im Tag</v>
+        <v>Verstärkung (Blenden)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>Basis</v>
+        <v>Kurve im Tag</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>Regler</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>Eingang = Display-Spitze</v>
+        <v>Regler</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>Graue Tonkurven nach Headroom</v>
+        <v>Eingang = Display-Spitze</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
+        <v>Graue Tonkurven nach Headroom</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} Blenden</v>
+        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} Blenden (Basis)</v>
+        <v>{h} Blenden</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>Bei {h} Blenden (Regler)</v>
+        <v>{h} Blenden (Basis)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Bei {h} Blenden (Regler)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Keine Änderung</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>Displays erkennen</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>Vollbereich</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>BERICHT</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>sie@example.com</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>(optional)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>Abbrechen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>Abonnieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>Schließen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Fehler:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,2949 +1197,2957 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Nach Namen sortieren</v>
+        <v>Zum Auswählen tippen, dann auf einen Tab tippen zum Senden.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Nach Namen sortieren</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Neues Profil aus .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und geöffnet; heruntergeladen wird erst, wenn Sie auf „ICC-Profil speichern“ klicken.</v>
+        <v>Neues Profil aus .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>.cube-Datei wählen</v>
+        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und geöffnet; heruntergeladen wird erst, wenn Sie auf „ICC-Profil speichern“ klicken.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>.cube-Datei wählen</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>oder hierher ziehen oder unten einfügen</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Abbrechen</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Wird erstellt…</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profil</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Vergleichen</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Verknüpfen</v>
+        <v>Vergleichen</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spektral</v>
+        <v>Verknüpfen</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Entfernen</v>
+        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Kein Profil ausgewählt</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
+        <v>Kein Profil ausgewählt</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Noch nichts zu vergleichen</v>
+        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
+        <v>Noch nichts zu vergleichen</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Gamut-Vergleich</v>
+        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
+        <v>Gamut-Vergleich</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Render-Intent</v>
+        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Hülle</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Drahtgitter</v>
+        <v>Hülle</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Achsenwerte</v>
+        <v>Drahtgitter</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Deckkraft</v>
+        <v>Achsenwerte</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Farbe</v>
+        <v>Deckkraft</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Einfarbig</v>
+        <v>Farbe</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Nach Wert</v>
+        <v>Einfarbig</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Nach Farbton</v>
+        <v>Nach Wert</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotation</v>
+        <v>Nach Farbton</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Drehteller</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Orbit</v>
+        <v>Drehteller</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Ziehgeschwindigkeit</v>
+        <v>Orbit</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rollen</v>
+        <v>Ziehgeschwindigkeit</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Rollgeschwindigkeit</v>
+        <v>Rollen</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Gamut wird erstellt…</v>
+        <v>Rollgeschwindigkeit</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>kein Gamut</v>
+        <v>Gamut wird erstellt…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Ein-/ausblenden</v>
+        <v>kein Gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D-Gamut-Hülle</v>
+        <v>Ein-/ausblenden</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D-Gamut-Schnitt</v>
+        <v>3D-Gamut-Hülle</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Ebene</v>
+        <v>2D-Gamut-Schnitt</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Ebene</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Verknüpfung</v>
+        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
+        <v>Verknüpfung</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
+        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4-Display-Ersteller</v>
+        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
+        <v>V4-Display-Ersteller</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5-RGB-Display</v>
+        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>Displayprofil ablegen</v>
+        <v>V5-RGB-Display</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5-Beobachter (PCC)</v>
+        <v>Displayprofil ablegen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>Beobachterprofil ablegen</v>
+        <v>V5-Beobachter (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
+        <v>Beobachterprofil ablegen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>V4-Displayprofil erstellen</v>
+        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Profilname</v>
+        <v>V4-Displayprofil erstellen</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Erstellen</v>
+        <v>Profilname</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Wird erstellt…</v>
+        <v>Erstellen</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Link-Pipeline</v>
+        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
+        <v>Link-Pipeline</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Fertig</v>
+        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
+        <v>Fertig</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Bild wird geprüft…</v>
+        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
+        <v>Bild wird geprüft…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
+        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Bild transformieren</v>
+        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Wird transformiert…</v>
+        <v>Bild transformieren</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Profile ablegen, um die Kette zu starten</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>entfernt</v>
+        <v>Profile ablegen, um die Kette zu starten</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Nach vorne verschieben</v>
+        <v>entfernt</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Nach hinten verschieben</v>
+        <v>Nach vorne verschieben</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Nach oben verschieben</v>
+        <v>Nach hinten verschieben</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Nach unten verschieben</v>
+        <v>Nach oben verschieben</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Rendering-Priorität (alle)</v>
+        <v>Nach unten verschieben</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Rendering-Priorität für diese Transformation</v>
+        <v>Rendering-Priorität (alle)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
+        <v>Rendering-Priorität für diese Transformation</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
+        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
+        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Kette</v>
+        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Die Kette konnte nicht analysiert werden.</v>
+        <v>Kette</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Kette wird geprüft…</v>
+        <v>Die Kette konnte nicht analysiert werden.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>Die Kette verbindet sich nicht ({detail}).</v>
+        <v>Kette wird geprüft…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
+        <v>Die Kette verbindet sich nicht ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
+        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Leeren</v>
+        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink-Name</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Wird erstellt…</v>
+        <v>DeviceLink-Name</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
+        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
+        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
+        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformiertes Bild gespeichert.</v>
+        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformiertes Bild gespeichert.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Datendatei zu groß.</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Daten transformieren</v>
+        <v>Datendatei zu groß.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Wird transformiert…</v>
+        <v>Daten transformieren</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Bevorzugen</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Beobachter</v>
+        <v>Bevorzugen</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Lichtart</v>
+        <v>Beobachter</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Bedingung</v>
+        <v>Lichtart</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} Duplikat(e) filtern</v>
+        <v>Bedingung</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>Median</v>
+        <v>{n} Duplikat(e) filtern</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>Mittelwert</v>
+        <v>Median</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>Farbfelder</v>
+        <v>Mittelwert</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} Duplikate</v>
+        <v>Farbfelder</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Transformationsergebnis</v>
+        <v>{n} Duplikate</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} Farbfelder</v>
+        <v>Transformationsergebnis</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
+        <v>{src} → {dst} · {n} Farbfelder</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Speichern unter</v>
+        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Speichern</v>
+        <v>Speichern unter</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Transformation umkehren</v>
+        <v>Speichern</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Wird umgekehrt…</v>
+        <v>Transformation umkehren</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Umkehren</v>
+        <v>Wird umgekehrt…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>letzte Stufe</v>
+        <v>Umkehren</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>erste Stufe</v>
+        <v>letzte Stufe</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Daten in {in} → Suche {out}</v>
+        <v>erste Stufe</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
+        <v>Daten in {in} → Suche {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
+        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE-Kosten</v>
+        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
+        <v>ΔE-Kosten</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extrahieren &amp; zur Kette hinzufügen</v>
+        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Wird extrahiert…</v>
+        <v>Extrahieren &amp; zur Kette hinzufügen</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Verwerfen</v>
+        <v>Wird extrahiert…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
+        <v>Verwerfen</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Bildausgabeoptionen</v>
+        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Kodierung</v>
+        <v>Bildausgabeoptionen</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Wie Quelle</v>
+        <v>Kodierung</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 Bit</v>
+        <v>Wie Quelle</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 Bit</v>
+        <v>8 Bit</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Gleitkomma (32 Bit)</v>
+        <v>16 Bit</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Komprimierung</v>
+        <v>Gleitkomma (32 Bit)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Keine</v>
+        <v>Komprimierung</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planar</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Verschachtelt</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Getrennt</v>
+        <v>Verschachtelt</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM-Interpolation</v>
+        <v>Getrennt</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraedrisch</v>
+        <v>CMM-Interpolation</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linear</v>
+        <v>Tetraedrisch</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>ICC-Profil einbetten</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
+        <v>ICC-Profil einbetten</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Spektrales TIFF zusammenstellen</v>
+        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
+        <v>Spektrales TIFF zusammenstellen</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
+        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>Kan</v>
+        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Zusammenfügen &amp; Speichern</v>
+        <v>Kan</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Wird zusammengefügt…</v>
+        <v>Zusammenfügen &amp; Speichern</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n} Kanäle zusammengefügt.</v>
+        <v>Wird zusammengefügt…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
+        <v>{n} Kanäle zusammengefügt.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Abbrechen</v>
+        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} Datei(en) nicht geladen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
+        <v>{n} Datei(en) nicht geladen</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>oder</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Datei wählen</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Header</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validierung</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analyse</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Render-Intent</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% Farbe</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* Ausgabe (Tonwert)</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* Ausgabe (Tonwert)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Kolorimetrie der Extremwerte</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Die Enden des Wiedergabeumfangs des Profils: das Weiß des Bedruckstoffs, das dunkelste Schwarz, das es druckt, der Farbauftrag, den dieses Schwarz kostet, und der Punkt, an dem jeder Farbton am gesättigtsten ist.</v>
+        <v>Kolorimetrie der Extremwerte</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Der Weißpunkt ist die Farbe bei null Farbmittel — der blanke Bedruckstoff. Der Schwarzpunkt ergibt sich, indem PCS-Schwarz (L*=0, a*=b*=0) durch die gewählte B2A-Tabelle geführt wird, um den Farbauftrag zu erhalten, den das Profil für Schwarz wählt, und dieser Farbauftrag anschließend über A2B1 zurückgelesen wird. Der Gesamtfarbauftrag (TAC) ist die Summe dieses Farbauftrags. Die absolute Kolorimetrie zeigt die Eigenfarbe des Bedruckstoffs; die relative bezieht sie auf ein perfektes Weiß.</v>
+        <v>Die Enden des Wiedergabeumfangs des Profils: das Weiß des Bedruckstoffs, das dunkelste Schwarz, das es druckt, der Farbauftrag, den dieses Schwarz kostet, und der Punkt, an dem jeder Farbton am gesättigtsten ist.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativ</v>
+        <v>Der Weißpunkt ist die Farbe bei null Farbmittel — der blanke Bedruckstoff. Der Schwarzpunkt ergibt sich, indem PCS-Schwarz (L*=0, a*=b*=0) durch die gewählte B2A-Tabelle geführt wird, um den Farbauftrag zu erhalten, den das Profil für Schwarz wählt, und dieser Farbauftrag anschließend über A2B1 zurückgelesen wird. Der Gesamtfarbauftrag (TAC) ist die Summe dieses Farbauftrags. Die absolute Kolorimetrie zeigt die Eigenfarbe des Bedruckstoffs; die relative bezieht sie auf ein perfektes Weiß.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absolut</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Weißpunkt</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Schwarzpunkt</v>
+        <v>Weißpunkt</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Farbauftrag am Schwarzpunkt</v>
+        <v>Schwarzpunkt</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Farbauftrag am Schwarzpunkt</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Dieses Profil hat kein Medien-Weißpunkt-Tag, daher ist die absolute Kolorimetrie nicht verfügbar.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>Die Kolorimetrie der Extremwerte ist nur für Ausgabeprofile (Drucker) verfügbar — sie setzt voraus, dass null Farbmittel dem blanken Bedruckstoff entspricht.</v>
+        <v>Dieses Profil hat kein Medien-Weißpunkt-Tag, daher ist die absolute Kolorimetrie nicht verfügbar.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Vollton gegenüber maximalem Chroma</v>
+        <v>Die Kolorimetrie der Extremwerte ist nur für Ausgabeprofile (Drucker) verfügbar — sie setzt voraus, dass null Farbmittel dem blanken Bedruckstoff entspricht.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Wo jede Farbecke landet und der farbigste Punkt auf dem Weg dorthin. Gemessen über A2B1, daher ändern sich diese Zeilen nicht mit dem Render-Intent oben. Bei einem gutmütigen Profil stimmen beide Zeilen überein; wird das maximale Chroma vor dem Vollton erreicht, verdunkelt die Farbe darüber hinaus nur noch.</v>
+        <v>Vollton gegenüber maximalem Chroma</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Farbton</v>
+        <v>Wo jede Farbecke landet und der farbigste Punkt auf dem Weg dorthin. Gemessen über A2B1, daher ändern sich diese Zeilen nicht mit dem Render-Intent oben. Bei einem gutmütigen Profil stimmen beide Zeilen überein; wird das maximale Chroma vor dem Vollton erreicht, verdunkelt die Farbe darüber hinaus nur noch.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Vollton</v>
+        <v>Farbton</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>Max. C*</v>
+        <v>Vollton</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Bei Farbauftrag</v>
+        <v>Max. C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>Das maximale Chroma wird vor dem Vollton erreicht — Farbe darüber hinaus verdunkelt nur.</v>
+        <v>Bei Farbauftrag</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Farbverbrauch in den Tiefen</v>
+        <v>Das maximale Chroma wird vor dem Vollton erreicht — Farbe darüber hinaus verdunkelt nur.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Vier gerade Pfade durch die a*b*-Ebene bei einer konstanten, bewusst dunklen Helligkeit, geführt durch die gewählte B2A-Tabelle. Alle Abtastwerte teilen dieselbe L*, sodass jeder abrupte Sprung oder jede Umkehr eines Farbmittels allein aus der Behandlung von Farbton und Chroma stammt — die Signatur eines Gamut-Mapping-Artefakts in den Tiefen.</v>
+        <v>Farbverbrauch in den Tiefen</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>Der Farbverbrauch in den Tiefen ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Vier gerade Pfade durch die a*b*-Ebene bei einer konstanten, bewusst dunklen Helligkeit, geführt durch die gewählte B2A-Tabelle. Alle Abtastwerte teilen dieselbe L*, sodass jeder abrupte Sprung oder jede Umkehr eines Farbmittels allein aus der Behandlung von Farbton und Chroma stammt — die Signatur eines Gamut-Mapping-Artefakts in den Tiefen.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Ebene konstanter L*</v>
+        <v>Der Farbverbrauch in den Tiefen ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>schwarzpunktkompensiert ab</v>
+        <v>Ebene konstanter L*</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Position entlang des Pfades</v>
+        <v>schwarzpunktkompensiert ab</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Pfad</v>
+        <v>Position entlang des Pfades</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Primärfarben-Pfade durch Neutral</v>
+        <v>Pfad</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Drei Pfade im Gamut — Cyan→Rot, Magenta→Grün, Gelb→Blau — jeder durch die Neutralachse bei der mittleren Helligkeit seiner Endpunkte, durch die gewählte B2A-Tabelle geführt. Jeder Messpunkt liegt im Gamut, daher ist – anders als bei den Schattenpfaden – jede abrupte Stufe oder Umkehr eines Farbmittels ein CLUT-Glättungsfehler und kein Gamut-Mapping-Artefakt.</v>
+        <v>Primärfarben-Pfade durch Neutral</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Primärfarben-Pfade sind nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Drei Pfade im Gamut — Cyan→Rot, Magenta→Grün, Gelb→Blau — jeder durch die Neutralachse bei der mittleren Helligkeit seiner Endpunkte, durch die gewählte B2A-Tabelle geführt. Jeder Messpunkt liegt im Gamut, daher ist – anders als bei den Schattenpfaden – jede abrupte Stufe oder Umkehr eines Farbmittels ein CLUT-Glättungsfehler und kein Gamut-Mapping-Artefakt.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Position entlang des Pfades (Neutral in der Mitte)</v>
+        <v>Primärfarben-Pfade sind nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Schwarzpunktkompensation für diese Absicht angewendet.</v>
+        <v>Position entlang des Pfades (Neutral in der Mitte)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Farbverbrauchsstatistik</v>
+        <v>Schwarzpunktkompensation für diese Absicht angewendet.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Wie viel von jedem Farbmittel das Profil aufträgt, als Summe und als Anteil am Gesamtwert — die Farbverbrauchssignatur der Separation.</v>
+        <v>Farbverbrauchsstatistik</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Die Farbverbrauchsstatistik ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Wie viel von jedem Farbmittel das Profil aufträgt, als Summe und als Anteil am Gesamtwert — die Farbverbrauchssignatur der Separation.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Neutralachse</v>
+        <v>Die Farbverbrauchsstatistik ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Mittlere Deckung</v>
+        <v>Neutralachse</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Farbanteil</v>
+        <v>Mittlere Deckung</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>Der Farbanteil ist der Fingerabdruck des Neutralaufbaus — der Anteil jedes Farbmittels an der gesamten aufgetragenen Farbe, unabhängig von der Anzahl der Messpunkte.</v>
+        <v>Farbanteil</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Punkte im Gamut</v>
+        <v>Der Farbanteil ist der Fingerabdruck des Neutralaufbaus — der Anteil jedes Farbmittels an der gesamten aufgetragenen Farbe, unabhängig von der Anzahl der Messpunkte.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>Der Farbverbrauch über alle Gamut-Farben benötigt die B2A-Gamutgrenze, die noch nicht implementiert ist — ausstehend.</v>
+        <v>Punkte im Gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Keine Farbmitteldaten zum Zusammenfassen.</v>
+        <v>Der Farbverbrauch über alle Gamut-Farben benötigt die B2A-Gamutgrenze, die noch nicht implementiert ist — ausstehend.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Wählen Sie unten eine B2A-Tabelle (PCS→Gerät), um auch ein Graustufenbild der Farbdeckung für jedes Farbmittel anzuzeigen.</v>
+        <v>Keine Farbmitteldaten zum Zusammenfassen.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Farbdeckung jedes Farbmittels über dasselbe Gitter (dunkler = mehr Farbe).</v>
+        <v>Wählen Sie unten eine B2A-Tabelle (PCS→Gerät), um auch ein Graustufenbild der Farbdeckung für jedes Farbmittel anzuzeigen.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cyan</v>
+        <v>Farbdeckung jedes Farbmittels über dasselbe Gitter (dunkler = mehr Farbe).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Gelb</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rot</v>
+        <v>Gelb</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Grün</v>
+        <v>Rot</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Blau</v>
+        <v>Grün</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Schwarz</v>
+        <v>Blau</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perzeptiv</v>
+        <v>Schwarz</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Sättigung</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Profilstatistik</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Render-Intent</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>Mittel</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>Max.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analyse läuft…</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analyse</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Diagramm</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Rohausgabe</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Kurven</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Eingangskurven</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Ausgangskurven</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT-Bild</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Gamut-Bild</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Chromazität</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Streudiagramm</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Tonwertkurve</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Kurventabelle</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabellen</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Daten</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Auswerten</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Wird geladen…</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Eingang</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Ausgang</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Gleitkomma</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Gitterpunkt</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalisiert</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Lesbar</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Gerät → PCS</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Gerät</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Wird geladen…</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Sicherheit</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Konformität</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualität</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>BERICHT</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>sie@example.com</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>(optional)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>Abbrechen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>Abonnieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>Schließen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>Fehler:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3475,26 +3475,26 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR-Profil in der Kette</v>
+        <v>HDR-ColorSpace-Profil in der Kette</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Transformationen über ein HDR-Profil nutzen dessen AToB0Tag — das von Abschnitt 8.10.6 geforderte feste SDR-Rendering — da Abschnitt 8.10.1 keine TRC-Tags zulässt. Das Ergebnis ist dieser Rückfall, kein HDR-Verhalten.</v>
+        <v>Transformationen über ein HDR-ColorSpace-Profil nutzen dessen AToB0Tag — das von Abschnitt 8.7.1.5 geforderte feste SDR-Rendering — da ein ColorSpace-Profil keine TRC-Tags besitzt. Das Ergebnis ist dieser Rückfall, kein HDR-Verhalten.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Dies sind HDR-Profile ohne TRC-Tags; der Gamut wird daher aus dem AToB0Tag gebildet — dem festen SDR-Rendering, das Abschnitt 8.10.6 für Anwendungen ohne HDR-Verarbeitung verlangt. Es ist nicht der HDR-Gamut des Profils, der in einem begrenzten PCS nicht darstellbar ist.</v>
+        <v>Dies sind HDR-ColorSpace-Profile ohne TRC-Tags; der Gamut wird daher aus dem AToB0Tag gebildet — dem festen SDR-Rendering, das Abschnitt 8.7.1.5 für Anwendungen ohne HDR-Verarbeitung verlangt. Es ist nicht der HDR-Gamut des Profils, der in einem begrenzten PCS nicht darstellbar ist.</v>
       </c>
     </row>
     <row r="387">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Datei 1,0 = 1 cd/m² (ICC.1 Abschnitt 8.10.2 a)</v>
+        <v>Datei 1,0 = 1 cd/m² (ICC.1 Abschnitt 8.7.1.2 a)</v>
       </c>
     </row>
     <row r="532">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Auto (Rangfolge nach 8.10.3)</v>
+        <v>Auto (Rangfolge nach 8.7.1.3)</v>
       </c>
     </row>
     <row r="540">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>HDR-Profile</v>
+        <v>HDR-ColorSpace-Profile</v>
       </c>
     </row>
     <row r="548">
@@ -4803,1263 +4803,1271 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR-Profile – lineare Übertragung</v>
+        <v>HDR-ColorSpace-Profile – lineare Übertragung</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>HDR-Profile – PQ-/HLG-Übertragung</v>
+        <v>HDR-ColorSpace-Profile – PQ-/HLG-Übertragung</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format} enthält lineares Licht, daher können nur HDR-Profile mit linearer Übertragung zugewiesen werden.</v>
+        <v>{format} enthält lineares Licht, daher können nur HDR-ColorSpace-Profile mit linearer Übertragung zugewiesen werden.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>{n} PQ/HLG-HDR-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-Profile › Nichtlineare Übertragung.</v>
+        <v>{n} PQ/HLG-HDR-ColorSpace-Profil(e) im Pool werden nicht angeboten – der Profilbereich führt sie unter HDR-ColorSpace-Profile › Nichtlineare Übertragung.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>Noch kein HDR-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-Profile nach Übertragung.</v>
+        <v>Noch kein HDR-ColorSpace-Profil mit linearer Übertragung im Pool; der Profilbereich gruppiert HDR-ColorSpace-Profile nach Übertragung.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.10.3).</v>
+        <v>Nicht spezifizierte Primärfarben: kein HDR-Pfad in diesem Build</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>Display-Spielraum</v>
+        <v>IccProfLib wendet diese Verstärkungskurve nicht an: {why}. Ein CMM greift auf den nächsten Tone-Mapping-Deskriptor zurück (Abschnitt 8.7.1.3).</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
+        <v>Display-Spielraum</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>Basis</v>
+        <v>{n} Blendenstufen (≈{r}× Referenzweiß)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>Vorschau durch das Farbmodul</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
+        <v>Vorschau durch das Farbmodul</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>Tonemapping für {h} Blenden</v>
+        <v>Wie erstellt (Basis {h} Blenden, ohne Verstärkung)</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
+        <v>Tonemapping für {h} Blenden</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>Referenzweiß</v>
+        <v>Dieselben Testpixel ({transfer}-Signal von links nach rechts steigend: Grau, dann R, G, B, Y, C, M) durch die HDR-Transformation von IccProfLib. Beide Streifen sind auf das {r}-Fache des HDR-Referenzweiß begrenzt, wie ein Display mit {h} Blenden Headroom sie zeigen würde: Wo der obere Streifen flach clippt, rollt die Gain-Kurve die Lichter ab.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>Display-Spitze</v>
+        <v>Referenzweiß</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>Vorschau nicht verfügbar: {why}</v>
+        <v>Display-Spitze</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
+        <v>Vorschau nicht verfügbar: {why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>Verstärkung über alle Headrooms</v>
+        <v>das Farbmodul hat für dieses Profil nicht den HDR-Pfad genommen</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
+        <v>Verstärkung über alle Headrooms</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Verstärkung für einen grauen Eingang bei jedem Display-Headroom: Blau komprimiert, Rot expandiert, Weiß lässt ihn unverändert. Gepunktete Linien markieren die Kurven im Tag, die durchgezogene die Basis, die bernsteinfarbene den Regler; die gestrichelte Diagonale ist dort, wo der Eingang die Display-Spitze erreicht. Klicken setzt den Regler.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>Display-Headroom (Blenden)</v>
+        <v>Eingang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Verstärkung (Blenden)</v>
+        <v>Display-Headroom (Blenden)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>Kurve im Tag</v>
+        <v>Verstärkung (Blenden)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>Basis</v>
+        <v>Kurve im Tag</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>Regler</v>
+        <v>Basis</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>Eingang = Display-Spitze</v>
+        <v>Regler</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>Graue Tonkurven nach Headroom</v>
+        <v>Eingang = Display-Spitze</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
+        <v>Graue Tonkurven nach Headroom</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
+        <v>Die graue Tonkurve bei jedem im Tag gespeicherten Headroom, von niedrig (blau) bis hoch (rot) eingefärbt, die Kurve des Reglers in Bernstein. Beide Achsen sind in Blenden, die Diagonale bedeutet keine Änderung.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} Blenden</v>
+        <v>Ausgang (Blenden relativ zum HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} Blenden (Basis)</v>
+        <v>{h} Blenden</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>Bei {h} Blenden (Regler)</v>
+        <v>{h} Blenden (Basis)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
+        <v>Bei {h} Blenden (Regler)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
+        <v>Kurven im Tag nach Spielraum: {list} Blendenstufen. Basis {b} Blendenstufen, HDR-Referenzweiß {w} cd/m².</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
+        <v>Dieser Spielraum liegt außerhalb der Kurven im Tag; die nächstgelegene Kurve wird unverändert verwendet – die Bibliothek extrapoliert nicht darüber hinaus.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
+        <v>Einige Steigungen sind abgeleitet (PCHIP) und nicht im Tag gespeichert. Diese Ableitung rekonstruiert einen SMPTE-Abschnitt; die Form dieser Kurven gilt daher als vorläufig.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
+        <v>Der Tag verlangt Tone-Mapping auf Referenzweiß; seine Kurven werden daher von der Bibliothek konstruiert statt aus der Datei gelesen (eine Konstruktion aus einem Komitee-Entwurf).</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
+        <v>Keine alternativen Bilder: Der Tag verlangt kein Tone-Mapping, nur eine Begrenzung auf das Farbvolumen des Displays.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
+        <v>Die beiden bei diesem Spielraum gemischten Kurven mischen die Farbkanäle unterschiedlich; es gibt daher keine einzelne Verstärkungskurve. Die Tonkurve unten ist trotzdem exakt.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>Kurve bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen (keine Verstärkung)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Angewendet bei {h} Blendenstufen</v>
+        <v>Kurve bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>Verstärkung bei diesem Spielraum</v>
+        <v>Angewendet bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
+        <v>Verstärkung bei diesem Spielraum</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>Verstärkung (log2-Blendenstufen)</v>
+        <v>Gemischter Eingang (linear, 1,0 = HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
+        <v>Verstärkung (log2-Blendenstufen)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>Eingang (× HDR-Referenzweiß)</v>
+        <v>Graustufen-Tonkurve bei diesem Spielraum</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Ausgang (× HDR-Referenzweiß)</v>
+        <v>Eingang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>Keine Änderung</v>
+        <v>Ausgang (× HDR-Referenzweiß)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>Display-Spitze bei {h} Blendenstufen</v>
+        <v>Keine Änderung</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>Ausgang bei {h} Blendenstufen</v>
+        <v>Display-Spitze bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
+        <v>Ausgang bei {h} Blendenstufen</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>Displays erkennen</v>
+        <v>HDR, Farbraum und Pixelverhältnis werden aktualisiert, wenn das Fenster auf einen Bildschirm wechselt, auf dem sie abweichen.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
+        <v>Displays erkennen</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
+        <v>Fragt die Erlaubnis, zu sehen, auf welchem Monitor dieses Fenster liegt – so aktualisiert sich das Panel auch zwischen gleich wirkenden Bildschirmen und zeigt den HDR-Spielraum, wo der Browser ihn bereitstellt.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
+        <v>Verfolgt, auf welchem Monitor dieses Fenster liegt.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
+        <v>Die Erlaubnis zum Erkennen der Displays wurde verweigert. Sie lässt sich in den Einstellungen dieser Website ändern.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>Displays konnten nicht erkannt werden.</v>
+        <v>Dieser Browser kann Displays nicht erkennen; es gilt nur die automatische Aktualisierung oben.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>Display-Ereignisse</v>
+        <v>Displays konnten nicht erkannt werden.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
+        <v>Display-Ereignisse</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>Farbprimärvalenzen</v>
+        <v>Noch keine Ereignisse. Ziehen Sie das Fenster auf einen anderen Monitor.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>Übertragungsfunktion</v>
+        <v>Farbprimärvalenzen</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>Matrixkoeffizienten</v>
+        <v>Übertragungsfunktion</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>Video-Vollbereichs-Flag</v>
+        <v>Matrixkoeffizienten</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>Vollbereich</v>
+        <v>Video-Vollbereichs-Flag</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>Eingeschränkter Bereich</v>
+        <v>Vollbereich</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>von ITU-T H.273 nicht vergeben</v>
+        <v>Eingeschränkter Bereich</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
+        <v>von ITU-T H.273 nicht vergeben</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
+        <v>Farbprimärvalenzen 2 (Nicht spezifiziert) verweist auf das Profil selbst — die Primärvalenzen stammen aus den Farbmittel-Tags, nicht aus diesem Tag.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>BERICHT</v>
+        <v>Die vier reservierten Bytes dieses Tags sind nicht alle null.</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>sie@example.com</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>(optional)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>Abbrechen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>Abonnieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>Schließen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>Fehler:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B707"/>
   </ignoredErrors>
 </worksheet>
 </file>